--- a/research/traditional_assets/database/data/israel/israel_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_restaurant_dining.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1003918292511212</v>
+        <v>0.1001955780438436</v>
       </c>
       <c r="C2">
-        <v>62.53136849715008</v>
+        <v>62.11128299290792</v>
       </c>
       <c r="D2">
-        <v>59.29136849715008</v>
+        <v>59.50528299290792</v>
       </c>
       <c r="E2">
-        <v>-30.1</v>
+        <v>-29.466</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.634</v>
       </c>
       <c r="G2">
         <v>3.24</v>
@@ -1439,28 +1439,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0318902</v>
       </c>
       <c r="N2">
-        <v>4.746666666666667</v>
+        <v>4.714776466666667</v>
       </c>
       <c r="O2">
-        <v>1.091733333333333</v>
+        <v>1.084398587333333</v>
       </c>
       <c r="P2">
-        <v>3.654933333333334</v>
+        <v>3.630377879333333</v>
       </c>
       <c r="Q2">
-        <v>6.474933333333334</v>
+        <v>6.450377879333334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1003918292511212</v>
+        <v>0.1008164323675188</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326223</v>
+        <v>0.8510867114033206</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>148.8440544953204</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1001955780438436</v>
+        <v>0.099999326836566</v>
       </c>
       <c r="C3">
-        <v>62.11128299290792</v>
+        <v>61.69274662148705</v>
       </c>
       <c r="D3">
-        <v>59.50528299290792</v>
+        <v>59.72074662148705</v>
       </c>
       <c r="E3">
-        <v>-29.466</v>
+        <v>-28.832</v>
       </c>
       <c r="F3">
-        <v>0.634</v>
+        <v>1.268</v>
       </c>
       <c r="G3">
         <v>3.24</v>
@@ -1521,28 +1521,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0318902</v>
+        <v>0.0637804</v>
       </c>
       <c r="N3">
-        <v>4.714776466666667</v>
+        <v>4.682886266666667</v>
       </c>
       <c r="O3">
-        <v>1.084398587333333</v>
+        <v>1.077063841333334</v>
       </c>
       <c r="P3">
-        <v>3.630377879333333</v>
+        <v>3.605822425333334</v>
       </c>
       <c r="Q3">
-        <v>6.450377879333334</v>
+        <v>6.425822425333334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1008164323675188</v>
+        <v>0.1012497008536388</v>
       </c>
       <c r="T3">
-        <v>0.8510867114033206</v>
+        <v>0.8577892370877065</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>148.8440544953204</v>
+        <v>74.42202724766021</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.099999326836566</v>
+        <v>0.09980307562928842</v>
       </c>
       <c r="C4">
-        <v>61.69274662148705</v>
+        <v>61.27577627188031</v>
       </c>
       <c r="D4">
-        <v>59.72074662148705</v>
+        <v>59.93777627188031</v>
       </c>
       <c r="E4">
-        <v>-28.832</v>
+        <v>-28.198</v>
       </c>
       <c r="F4">
-        <v>1.268</v>
+        <v>1.902</v>
       </c>
       <c r="G4">
         <v>3.24</v>
@@ -1603,28 +1603,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M4">
-        <v>0.0637804</v>
+        <v>0.09567059999999999</v>
       </c>
       <c r="N4">
-        <v>4.682886266666667</v>
+        <v>4.650996066666667</v>
       </c>
       <c r="O4">
-        <v>1.077063841333334</v>
+        <v>1.069729095333333</v>
       </c>
       <c r="P4">
-        <v>3.605822425333334</v>
+        <v>3.581266971333334</v>
       </c>
       <c r="Q4">
-        <v>6.425822425333334</v>
+        <v>6.401266971333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1012497008536388</v>
+        <v>0.1016919027106066</v>
       </c>
       <c r="T4">
-        <v>0.8577892370877065</v>
+        <v>0.8646299591779559</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>74.42202724766021</v>
+        <v>49.61468483177347</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09980307562928842</v>
+        <v>0.09960682442201083</v>
       </c>
       <c r="C5">
-        <v>61.27577627188031</v>
+        <v>60.86038907947948</v>
       </c>
       <c r="D5">
-        <v>59.93777627188031</v>
+        <v>60.15638907947947</v>
       </c>
       <c r="E5">
-        <v>-28.198</v>
+        <v>-27.564</v>
       </c>
       <c r="F5">
-        <v>1.902</v>
+        <v>2.536</v>
       </c>
       <c r="G5">
         <v>3.24</v>
@@ -1685,28 +1685,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M5">
-        <v>0.09567059999999999</v>
+        <v>0.1275608</v>
       </c>
       <c r="N5">
-        <v>4.650996066666667</v>
+        <v>4.619105866666667</v>
       </c>
       <c r="O5">
-        <v>1.069729095333333</v>
+        <v>1.062394349333333</v>
       </c>
       <c r="P5">
-        <v>3.581266971333334</v>
+        <v>3.556711517333333</v>
       </c>
       <c r="Q5">
-        <v>6.401266971333333</v>
+        <v>6.376711517333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1016919027106066</v>
+        <v>0.1021433171062613</v>
       </c>
       <c r="T5">
-        <v>0.8646299591779559</v>
+        <v>0.8716131963117523</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.61468483177347</v>
+        <v>37.2110136238301</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09960682442201083</v>
+        <v>0.09941057321473326</v>
       </c>
       <c r="C6">
-        <v>60.86038907947948</v>
+        <v>60.44660243058505</v>
       </c>
       <c r="D6">
-        <v>60.15638907947947</v>
+        <v>60.37660243058505</v>
       </c>
       <c r="E6">
-        <v>-27.564</v>
+        <v>-26.93</v>
       </c>
       <c r="F6">
-        <v>2.536</v>
+        <v>3.17</v>
       </c>
       <c r="G6">
         <v>3.24</v>
@@ -1767,28 +1767,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M6">
-        <v>0.1275608</v>
+        <v>0.159451</v>
       </c>
       <c r="N6">
-        <v>4.619105866666667</v>
+        <v>4.587215666666667</v>
       </c>
       <c r="O6">
-        <v>1.062394349333333</v>
+        <v>1.055059603333333</v>
       </c>
       <c r="P6">
-        <v>3.556711517333333</v>
+        <v>3.532156063333334</v>
       </c>
       <c r="Q6">
-        <v>6.376711517333334</v>
+        <v>6.352156063333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1021433171062613</v>
+        <v>0.1026042349628771</v>
       </c>
       <c r="T6">
-        <v>0.8716131963117523</v>
+        <v>0.878743448964155</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.2110136238301</v>
+        <v>29.76881089906409</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09941057321473326</v>
+        <v>0.09921432200745568</v>
       </c>
       <c r="C7">
-        <v>60.44660243058505</v>
+        <v>60.03443396701579</v>
       </c>
       <c r="D7">
-        <v>60.37660243058505</v>
+        <v>60.59843396701579</v>
       </c>
       <c r="E7">
-        <v>-26.93</v>
+        <v>-26.296</v>
       </c>
       <c r="F7">
-        <v>3.17</v>
+        <v>3.804</v>
       </c>
       <c r="G7">
         <v>3.24</v>
@@ -1849,28 +1849,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M7">
-        <v>0.159451</v>
+        <v>0.1913412</v>
       </c>
       <c r="N7">
-        <v>4.587215666666667</v>
+        <v>4.555325466666667</v>
       </c>
       <c r="O7">
-        <v>1.055059603333333</v>
+        <v>1.047724857333334</v>
       </c>
       <c r="P7">
-        <v>3.532156063333334</v>
+        <v>3.507600609333333</v>
       </c>
       <c r="Q7">
-        <v>6.352156063333334</v>
+        <v>6.327600609333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1026042349628771</v>
+        <v>0.1030749595823997</v>
       </c>
       <c r="T7">
-        <v>0.878743448964155</v>
+        <v>0.8860254091198002</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.76881089906409</v>
+        <v>24.80734241588673</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09921432200745567</v>
+        <v>0.0990180708001781</v>
       </c>
       <c r="C8">
-        <v>60.0344339670158</v>
+        <v>59.62390159081994</v>
       </c>
       <c r="D8">
-        <v>60.5984339670158</v>
+        <v>60.82190159081995</v>
       </c>
       <c r="E8">
-        <v>-26.296</v>
+        <v>-25.662</v>
       </c>
       <c r="F8">
-        <v>3.804</v>
+        <v>4.438</v>
       </c>
       <c r="G8">
         <v>3.24</v>
@@ -1931,28 +1931,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M8">
-        <v>0.1913412</v>
+        <v>0.2232314</v>
       </c>
       <c r="N8">
-        <v>4.555325466666667</v>
+        <v>4.523435266666667</v>
       </c>
       <c r="O8">
-        <v>1.047724857333334</v>
+        <v>1.040390111333333</v>
       </c>
       <c r="P8">
-        <v>3.507600609333333</v>
+        <v>3.483045155333333</v>
       </c>
       <c r="Q8">
-        <v>6.327600609333333</v>
+        <v>6.303045155333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1030749595823997</v>
+        <v>0.1035558073120195</v>
       </c>
       <c r="T8">
-        <v>0.8860254091198001</v>
+        <v>0.8934639705691151</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.80734241588674</v>
+        <v>21.26343635647435</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09901807080017809</v>
+        <v>0.09882181959290054</v>
       </c>
       <c r="C9">
-        <v>59.62390159081995</v>
+        <v>59.21502346909124</v>
       </c>
       <c r="D9">
-        <v>60.82190159081996</v>
+        <v>61.04702346909124</v>
       </c>
       <c r="E9">
-        <v>-25.662</v>
+        <v>-25.028</v>
       </c>
       <c r="F9">
-        <v>4.438000000000001</v>
+        <v>5.072</v>
       </c>
       <c r="G9">
         <v>3.24</v>
@@ -2013,28 +2013,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M9">
-        <v>0.2232314</v>
+        <v>0.2551216</v>
       </c>
       <c r="N9">
-        <v>4.523435266666667</v>
+        <v>4.491545066666667</v>
       </c>
       <c r="O9">
-        <v>1.040390111333333</v>
+        <v>1.033055365333333</v>
       </c>
       <c r="P9">
-        <v>3.483045155333333</v>
+        <v>3.458489701333334</v>
       </c>
       <c r="Q9">
-        <v>6.303045155333334</v>
+        <v>6.278489701333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1035558073120195</v>
+        <v>0.1040471082531527</v>
       </c>
       <c r="T9">
-        <v>0.8934639705691151</v>
+        <v>0.9010642398760239</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.26343635647434</v>
+        <v>18.60550681191505</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09882181959290054</v>
+        <v>0.09862556838562296</v>
       </c>
       <c r="C10">
-        <v>59.21502346909124</v>
+        <v>58.80781803889226</v>
       </c>
       <c r="D10">
-        <v>61.04702346909124</v>
+        <v>61.27381803889227</v>
       </c>
       <c r="E10">
-        <v>-25.028</v>
+        <v>-24.394</v>
       </c>
       <c r="F10">
-        <v>5.072</v>
+        <v>5.706</v>
       </c>
       <c r="G10">
         <v>3.24</v>
@@ -2095,28 +2095,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M10">
-        <v>0.2551216</v>
+        <v>0.2870118</v>
       </c>
       <c r="N10">
-        <v>4.491545066666667</v>
+        <v>4.459654866666667</v>
       </c>
       <c r="O10">
-        <v>1.033055365333333</v>
+        <v>1.025720619333333</v>
       </c>
       <c r="P10">
-        <v>3.458489701333334</v>
+        <v>3.433934247333333</v>
       </c>
       <c r="Q10">
-        <v>6.278489701333334</v>
+        <v>6.253934247333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1040471082531527</v>
+        <v>0.1045492070171681</v>
       </c>
       <c r="T10">
-        <v>0.9010642398760239</v>
+        <v>0.9088315480687991</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.60550681191505</v>
+        <v>16.53822827725782</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09862556838562296</v>
+        <v>0.09842931717834538</v>
       </c>
       <c r="C11">
-        <v>58.80781803889226</v>
+        <v>58.40230401228785</v>
       </c>
       <c r="D11">
-        <v>61.27381803889227</v>
+        <v>61.50230401228785</v>
       </c>
       <c r="E11">
-        <v>-24.394</v>
+        <v>-23.76</v>
       </c>
       <c r="F11">
-        <v>5.706</v>
+        <v>6.339999999999999</v>
       </c>
       <c r="G11">
         <v>3.24</v>
@@ -2177,28 +2177,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M11">
-        <v>0.2870118</v>
+        <v>0.3189019999999999</v>
       </c>
       <c r="N11">
-        <v>4.459654866666667</v>
+        <v>4.427764666666667</v>
       </c>
       <c r="O11">
-        <v>1.025720619333333</v>
+        <v>1.018385873333334</v>
       </c>
       <c r="P11">
-        <v>3.433934247333333</v>
+        <v>3.409378793333334</v>
       </c>
       <c r="Q11">
-        <v>6.253934247333333</v>
+        <v>6.229378793333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1045492070171681</v>
+        <v>0.1050624635314949</v>
       </c>
       <c r="T11">
-        <v>0.9088315480687991</v>
+        <v>0.9167714631103023</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.53822827725782</v>
+        <v>14.88440544953205</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09842931717834538</v>
+        <v>0.0982330659710678</v>
       </c>
       <c r="C12">
-        <v>58.40230401228784</v>
+        <v>57.99850038149167</v>
       </c>
       <c r="D12">
-        <v>61.50230401228785</v>
+        <v>61.73250038149168</v>
       </c>
       <c r="E12">
-        <v>-23.76</v>
+        <v>-23.126</v>
       </c>
       <c r="F12">
-        <v>6.34</v>
+        <v>6.974</v>
       </c>
       <c r="G12">
         <v>3.24</v>
@@ -2259,28 +2259,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M12">
-        <v>0.318902</v>
+        <v>0.3507922</v>
       </c>
       <c r="N12">
-        <v>4.427764666666667</v>
+        <v>4.395874466666667</v>
       </c>
       <c r="O12">
-        <v>1.018385873333334</v>
+        <v>1.011051127333334</v>
       </c>
       <c r="P12">
-        <v>3.409378793333334</v>
+        <v>3.384823339333334</v>
       </c>
       <c r="Q12">
-        <v>6.229378793333334</v>
+        <v>6.204823339333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1050624635314949</v>
+        <v>0.1055872539000762</v>
       </c>
       <c r="T12">
-        <v>0.9167714631103023</v>
+        <v>0.924889803208918</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.88440544953204</v>
+        <v>13.53127768139277</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0982330659710678</v>
+        <v>0.09817541476379021</v>
       </c>
       <c r="C13">
-        <v>57.99850038149167</v>
+        <v>57.43245121665561</v>
       </c>
       <c r="D13">
-        <v>61.73250038149168</v>
+        <v>61.80045121665562</v>
       </c>
       <c r="E13">
-        <v>-23.126</v>
+        <v>-22.492</v>
       </c>
       <c r="F13">
-        <v>6.974</v>
+        <v>7.608</v>
       </c>
       <c r="G13">
         <v>3.24</v>
@@ -2341,45 +2341,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M13">
-        <v>0.3507922</v>
+        <v>0.3940944</v>
       </c>
       <c r="N13">
-        <v>4.395874466666667</v>
+        <v>4.352572266666667</v>
       </c>
       <c r="O13">
-        <v>1.011051127333334</v>
+        <v>1.001091621333333</v>
       </c>
       <c r="P13">
-        <v>3.384823339333334</v>
+        <v>3.351480645333333</v>
       </c>
       <c r="Q13">
-        <v>6.204823339333334</v>
+        <v>6.171480645333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1055872539000762</v>
+        <v>0.1061239713224889</v>
       </c>
       <c r="T13">
-        <v>0.924889803208918</v>
+        <v>0.9331926510370476</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.23</v>
       </c>
       <c r="W13">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.53127768139277</v>
+        <v>12.04449153975968</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09817541476379021</v>
+        <v>0.09799071355651262</v>
       </c>
       <c r="C14">
-        <v>57.43245121665561</v>
+        <v>57.0171609673406</v>
       </c>
       <c r="D14">
-        <v>61.80045121665562</v>
+        <v>62.0191609673406</v>
       </c>
       <c r="E14">
-        <v>-22.492</v>
+        <v>-21.858</v>
       </c>
       <c r="F14">
-        <v>7.608</v>
+        <v>8.242000000000001</v>
       </c>
       <c r="G14">
         <v>3.24</v>
@@ -2423,28 +2423,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M14">
-        <v>0.3940944</v>
+        <v>0.4269356</v>
       </c>
       <c r="N14">
-        <v>4.352572266666667</v>
+        <v>4.319731066666667</v>
       </c>
       <c r="O14">
-        <v>1.001091621333333</v>
+        <v>0.9935381453333334</v>
       </c>
       <c r="P14">
-        <v>3.351480645333333</v>
+        <v>3.326192921333333</v>
       </c>
       <c r="Q14">
-        <v>6.171480645333334</v>
+        <v>6.146192921333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1061239713224889</v>
+        <v>0.1066730270764513</v>
       </c>
       <c r="T14">
-        <v>0.9331926510370476</v>
+        <v>0.9416863689301918</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.04449153975968</v>
+        <v>11.1179921905474</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09799071355651262</v>
+        <v>0.09780601234923504</v>
       </c>
       <c r="C15">
-        <v>57.0171609673406</v>
+        <v>56.60342422898208</v>
       </c>
       <c r="D15">
-        <v>62.0191609673406</v>
+        <v>62.23942422898209</v>
       </c>
       <c r="E15">
-        <v>-21.858</v>
+        <v>-21.224</v>
       </c>
       <c r="F15">
-        <v>8.242000000000001</v>
+        <v>8.876000000000001</v>
       </c>
       <c r="G15">
         <v>3.24</v>
@@ -2505,28 +2505,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M15">
-        <v>0.4269356</v>
+        <v>0.4597768</v>
       </c>
       <c r="N15">
-        <v>4.319731066666667</v>
+        <v>4.286889866666667</v>
       </c>
       <c r="O15">
-        <v>0.9935381453333334</v>
+        <v>0.9859846693333334</v>
       </c>
       <c r="P15">
-        <v>3.326192921333333</v>
+        <v>3.300905197333333</v>
       </c>
       <c r="Q15">
-        <v>6.146192921333334</v>
+        <v>6.120905197333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1066730270764513</v>
+        <v>0.107234851568878</v>
       </c>
       <c r="T15">
-        <v>0.9416863689301918</v>
+        <v>0.9503776151464325</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.1179921905474</v>
+        <v>10.32384989122258</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09780601234923504</v>
+        <v>0.09781766114195747</v>
       </c>
       <c r="C16">
-        <v>56.60342422898208</v>
+        <v>55.95548638294883</v>
       </c>
       <c r="D16">
-        <v>62.23942422898209</v>
+        <v>62.22548638294884</v>
       </c>
       <c r="E16">
-        <v>-21.224</v>
+        <v>-20.59</v>
       </c>
       <c r="F16">
-        <v>8.876000000000001</v>
+        <v>9.510000000000002</v>
       </c>
       <c r="G16">
         <v>3.24</v>
@@ -2587,45 +2587,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M16">
-        <v>0.4597768</v>
+        <v>0.508785</v>
       </c>
       <c r="N16">
-        <v>4.286889866666667</v>
+        <v>4.237881666666667</v>
       </c>
       <c r="O16">
-        <v>0.9859846693333334</v>
+        <v>0.9747127833333333</v>
       </c>
       <c r="P16">
-        <v>3.300905197333333</v>
+        <v>3.263168883333333</v>
       </c>
       <c r="Q16">
-        <v>6.120905197333334</v>
+        <v>6.083168883333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.107234851568878</v>
+        <v>0.1078098954611264</v>
       </c>
       <c r="T16">
-        <v>0.9503776151464325</v>
+        <v>0.9592733612736435</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.23</v>
       </c>
       <c r="W16">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.32384989122258</v>
+        <v>9.329415502946562</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09781766114195747</v>
+        <v>0.0976460499346799</v>
       </c>
       <c r="C17">
-        <v>55.95548638294884</v>
+        <v>55.52745368142318</v>
       </c>
       <c r="D17">
-        <v>62.22548638294884</v>
+        <v>62.43145368142317</v>
       </c>
       <c r="E17">
-        <v>-20.59</v>
+        <v>-19.956</v>
       </c>
       <c r="F17">
-        <v>9.51</v>
+        <v>10.144</v>
       </c>
       <c r="G17">
         <v>3.24</v>
@@ -2669,28 +2669,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M17">
-        <v>0.5087849999999999</v>
+        <v>0.542704</v>
       </c>
       <c r="N17">
-        <v>4.237881666666667</v>
+        <v>4.203962666666667</v>
       </c>
       <c r="O17">
-        <v>0.9747127833333336</v>
+        <v>0.9669114133333335</v>
       </c>
       <c r="P17">
-        <v>3.263168883333334</v>
+        <v>3.237051253333334</v>
       </c>
       <c r="Q17">
-        <v>6.083168883333334</v>
+        <v>6.057051253333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1078098954611264</v>
+        <v>0.1083986308746189</v>
       </c>
       <c r="T17">
-        <v>0.9592733612736435</v>
+        <v>0.9683809108800737</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.329415502946565</v>
+        <v>8.746327034012403</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0976460499346799</v>
+        <v>0.09747443872740232</v>
       </c>
       <c r="C18">
-        <v>55.52745368142318</v>
+        <v>55.10078901785291</v>
       </c>
       <c r="D18">
-        <v>62.43145368142317</v>
+        <v>62.63878901785291</v>
       </c>
       <c r="E18">
-        <v>-19.956</v>
+        <v>-19.322</v>
       </c>
       <c r="F18">
-        <v>10.144</v>
+        <v>10.778</v>
       </c>
       <c r="G18">
         <v>3.24</v>
@@ -2751,28 +2751,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M18">
-        <v>0.542704</v>
+        <v>0.576623</v>
       </c>
       <c r="N18">
-        <v>4.203962666666667</v>
+        <v>4.170043666666667</v>
       </c>
       <c r="O18">
-        <v>0.9669114133333335</v>
+        <v>0.9591100433333335</v>
       </c>
       <c r="P18">
-        <v>3.237051253333334</v>
+        <v>3.210933623333334</v>
       </c>
       <c r="Q18">
-        <v>6.057051253333334</v>
+        <v>6.030933623333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1083986308746189</v>
+        <v>0.1090015526836172</v>
       </c>
       <c r="T18">
-        <v>0.9683809108800737</v>
+        <v>0.9777079195131648</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.746327034012403</v>
+        <v>8.231837208482261</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09747443872740232</v>
+        <v>0.09730282752012474</v>
       </c>
       <c r="C19">
-        <v>55.10078901785291</v>
+        <v>54.6755060674471</v>
       </c>
       <c r="D19">
-        <v>62.63878901785291</v>
+        <v>62.8475060674471</v>
       </c>
       <c r="E19">
-        <v>-19.322</v>
+        <v>-18.688</v>
       </c>
       <c r="F19">
-        <v>10.778</v>
+        <v>11.412</v>
       </c>
       <c r="G19">
         <v>3.24</v>
@@ -2833,28 +2833,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M19">
-        <v>0.576623</v>
+        <v>0.610542</v>
       </c>
       <c r="N19">
-        <v>4.170043666666667</v>
+        <v>4.136124666666667</v>
       </c>
       <c r="O19">
-        <v>0.9591100433333335</v>
+        <v>0.9513086733333336</v>
       </c>
       <c r="P19">
-        <v>3.210933623333334</v>
+        <v>3.184815993333334</v>
       </c>
       <c r="Q19">
-        <v>6.030933623333334</v>
+        <v>6.004815993333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1090015526836172</v>
+        <v>0.1096191799025912</v>
       </c>
       <c r="T19">
-        <v>0.9777079195131648</v>
+        <v>0.9872624161616972</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.231837208482261</v>
+        <v>7.774512919122136</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09730282752012474</v>
+        <v>0.09724825631284717</v>
       </c>
       <c r="C20">
-        <v>54.6755060674471</v>
+        <v>54.10816846820234</v>
       </c>
       <c r="D20">
-        <v>62.8475060674471</v>
+        <v>62.91416846820234</v>
       </c>
       <c r="E20">
-        <v>-18.688</v>
+        <v>-18.054</v>
       </c>
       <c r="F20">
-        <v>11.412</v>
+        <v>12.046</v>
       </c>
       <c r="G20">
         <v>3.24</v>
@@ -2915,45 +2915,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M20">
-        <v>0.6105419999999999</v>
+        <v>0.6540978</v>
       </c>
       <c r="N20">
-        <v>4.136124666666667</v>
+        <v>4.092568866666667</v>
       </c>
       <c r="O20">
-        <v>0.9513086733333336</v>
+        <v>0.9412908393333336</v>
       </c>
       <c r="P20">
-        <v>3.184815993333334</v>
+        <v>3.151278027333334</v>
       </c>
       <c r="Q20">
-        <v>6.004815993333334</v>
+        <v>5.971278027333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1096191799025912</v>
+        <v>0.1102520571763545</v>
       </c>
       <c r="T20">
-        <v>0.9872624161616972</v>
+        <v>0.9970528263077244</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.23</v>
       </c>
       <c r="W20">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.774512919122137</v>
+        <v>7.256814908514702</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09724825631284717</v>
+        <v>0.09708280510556959</v>
       </c>
       <c r="C21">
-        <v>54.10816846820234</v>
+        <v>53.67714537452603</v>
       </c>
       <c r="D21">
-        <v>62.91416846820234</v>
+        <v>63.11714537452603</v>
       </c>
       <c r="E21">
-        <v>-18.054</v>
+        <v>-17.42</v>
       </c>
       <c r="F21">
-        <v>12.046</v>
+        <v>12.68</v>
       </c>
       <c r="G21">
         <v>3.24</v>
@@ -2997,28 +2997,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M21">
-        <v>0.6540978</v>
+        <v>0.688524</v>
       </c>
       <c r="N21">
-        <v>4.092568866666667</v>
+        <v>4.058142666666667</v>
       </c>
       <c r="O21">
-        <v>0.9412908393333336</v>
+        <v>0.9333728133333334</v>
       </c>
       <c r="P21">
-        <v>3.151278027333334</v>
+        <v>3.124769853333333</v>
       </c>
       <c r="Q21">
-        <v>5.971278027333334</v>
+        <v>5.944769853333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1102520571763545</v>
+        <v>0.110900756381962</v>
       </c>
       <c r="T21">
-        <v>0.9970528263077244</v>
+        <v>1.007087996707402</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.256814908514702</v>
+        <v>6.893974163088965</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09708280510556959</v>
+        <v>0.09691735389829201</v>
       </c>
       <c r="C22">
-        <v>53.67714537452603</v>
+        <v>53.24743622891783</v>
       </c>
       <c r="D22">
-        <v>63.11714537452603</v>
+        <v>63.32143622891783</v>
       </c>
       <c r="E22">
-        <v>-17.42</v>
+        <v>-16.786</v>
       </c>
       <c r="F22">
-        <v>12.68</v>
+        <v>13.314</v>
       </c>
       <c r="G22">
         <v>3.24</v>
@@ -3079,28 +3079,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M22">
-        <v>0.688524</v>
+        <v>0.7229502000000001</v>
       </c>
       <c r="N22">
-        <v>4.058142666666667</v>
+        <v>4.023716466666666</v>
       </c>
       <c r="O22">
-        <v>0.9333728133333334</v>
+        <v>0.9254547873333333</v>
       </c>
       <c r="P22">
-        <v>3.124769853333333</v>
+        <v>3.098261679333333</v>
       </c>
       <c r="Q22">
-        <v>5.944769853333334</v>
+        <v>5.918261679333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.110900756381962</v>
+        <v>0.1115658783522684</v>
       </c>
       <c r="T22">
-        <v>1.007087996707402</v>
+        <v>1.017377222053907</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.893974163088965</v>
+        <v>6.565689679132347</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09691735389829201</v>
+        <v>0.09675190269101443</v>
       </c>
       <c r="C23">
-        <v>53.24743622891783</v>
+        <v>52.81905383134883</v>
       </c>
       <c r="D23">
-        <v>63.32143622891783</v>
+        <v>63.52705383134884</v>
       </c>
       <c r="E23">
-        <v>-16.786</v>
+        <v>-16.152</v>
       </c>
       <c r="F23">
-        <v>13.314</v>
+        <v>13.948</v>
       </c>
       <c r="G23">
         <v>3.24</v>
@@ -3161,28 +3161,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M23">
-        <v>0.7229502</v>
+        <v>0.7573764000000001</v>
       </c>
       <c r="N23">
-        <v>4.023716466666667</v>
+        <v>3.989290266666667</v>
       </c>
       <c r="O23">
-        <v>0.9254547873333335</v>
+        <v>0.9175367613333334</v>
       </c>
       <c r="P23">
-        <v>3.098261679333334</v>
+        <v>3.071753505333334</v>
       </c>
       <c r="Q23">
-        <v>5.918261679333334</v>
+        <v>5.891753505333334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1115658783522684</v>
+        <v>0.1122480547320698</v>
       </c>
       <c r="T23">
-        <v>1.017377222053907</v>
+        <v>1.027930273691348</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.565689679132348</v>
+        <v>6.267249239171787</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09675190269101443</v>
+        <v>0.09676355148373685</v>
       </c>
       <c r="C24">
-        <v>52.81905383134883</v>
+        <v>52.17053338564201</v>
       </c>
       <c r="D24">
-        <v>63.52705383134884</v>
+        <v>63.51253338564201</v>
       </c>
       <c r="E24">
-        <v>-16.152</v>
+        <v>-15.518</v>
       </c>
       <c r="F24">
-        <v>13.948</v>
+        <v>14.582</v>
       </c>
       <c r="G24">
         <v>3.24</v>
@@ -3243,45 +3243,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M24">
-        <v>0.7573764000000001</v>
+        <v>0.8063846000000001</v>
       </c>
       <c r="N24">
-        <v>3.989290266666667</v>
+        <v>3.940282066666667</v>
       </c>
       <c r="O24">
-        <v>0.9175367613333334</v>
+        <v>0.9062648753333333</v>
       </c>
       <c r="P24">
-        <v>3.071753505333334</v>
+        <v>3.034017191333334</v>
       </c>
       <c r="Q24">
-        <v>5.891753505333334</v>
+        <v>5.854017191333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1122480547320698</v>
+        <v>0.112947949978879</v>
       </c>
       <c r="T24">
-        <v>1.027930273691348</v>
+        <v>1.038757430566126</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.23</v>
       </c>
       <c r="W24">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.267249239171787</v>
+        <v>5.886355799288164</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09676355148373685</v>
+        <v>0.09660580027645926</v>
       </c>
       <c r="C25">
-        <v>52.17053338564201</v>
+        <v>51.73373879849493</v>
       </c>
       <c r="D25">
-        <v>63.51253338564201</v>
+        <v>63.70973879849493</v>
       </c>
       <c r="E25">
-        <v>-15.518</v>
+        <v>-14.884</v>
       </c>
       <c r="F25">
-        <v>14.582</v>
+        <v>15.216</v>
       </c>
       <c r="G25">
         <v>3.24</v>
@@ -3325,28 +3325,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M25">
-        <v>0.8063846000000001</v>
+        <v>0.8414448000000001</v>
       </c>
       <c r="N25">
-        <v>3.940282066666667</v>
+        <v>3.905221866666667</v>
       </c>
       <c r="O25">
-        <v>0.9062648753333333</v>
+        <v>0.8982010293333335</v>
       </c>
       <c r="P25">
-        <v>3.034017191333334</v>
+        <v>3.007020837333334</v>
       </c>
       <c r="Q25">
-        <v>5.854017191333334</v>
+        <v>5.827020837333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.112947949978879</v>
+        <v>0.1136662635216569</v>
       </c>
       <c r="T25">
-        <v>1.038757430566126</v>
+        <v>1.049869512621818</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.886355799288164</v>
+        <v>5.641090974317824</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09660580027645926</v>
+        <v>0.09644804906918168</v>
       </c>
       <c r="C26">
-        <v>51.73373879849493</v>
+        <v>51.29817266506053</v>
       </c>
       <c r="D26">
-        <v>63.70973879849493</v>
+        <v>63.90817266506053</v>
       </c>
       <c r="E26">
-        <v>-14.884</v>
+        <v>-14.25</v>
       </c>
       <c r="F26">
-        <v>15.216</v>
+        <v>15.85</v>
       </c>
       <c r="G26">
         <v>3.24</v>
@@ -3407,28 +3407,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M26">
-        <v>0.8414448</v>
+        <v>0.876505</v>
       </c>
       <c r="N26">
-        <v>3.905221866666667</v>
+        <v>3.870161666666667</v>
       </c>
       <c r="O26">
-        <v>0.8982010293333335</v>
+        <v>0.8901371833333335</v>
       </c>
       <c r="P26">
-        <v>3.007020837333334</v>
+        <v>2.980024483333334</v>
       </c>
       <c r="Q26">
-        <v>5.827020837333334</v>
+        <v>5.800024483333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1136662635216569</v>
+        <v>0.1144037320922422</v>
       </c>
       <c r="T26">
-        <v>1.049869512621818</v>
+        <v>1.061277916865662</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.641090974317825</v>
+        <v>5.415447335345112</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09644804906918168</v>
+        <v>0.0962902978619041</v>
       </c>
       <c r="C27">
-        <v>51.29817266506053</v>
+        <v>50.86384649983155</v>
       </c>
       <c r="D27">
-        <v>63.90817266506053</v>
+        <v>64.10784649983155</v>
       </c>
       <c r="E27">
-        <v>-14.25</v>
+        <v>-13.616</v>
       </c>
       <c r="F27">
-        <v>15.85</v>
+        <v>16.484</v>
       </c>
       <c r="G27">
         <v>3.24</v>
@@ -3489,28 +3489,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M27">
-        <v>0.876505</v>
+        <v>0.9115652000000001</v>
       </c>
       <c r="N27">
-        <v>3.870161666666667</v>
+        <v>3.835101466666667</v>
       </c>
       <c r="O27">
-        <v>0.8901371833333335</v>
+        <v>0.8820733373333335</v>
       </c>
       <c r="P27">
-        <v>2.980024483333334</v>
+        <v>2.953028129333334</v>
       </c>
       <c r="Q27">
-        <v>5.800024483333334</v>
+        <v>5.773028129333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1144037320922422</v>
+        <v>0.1151611322458164</v>
       </c>
       <c r="T27">
-        <v>1.061277916865662</v>
+        <v>1.07299465635934</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.415447335345112</v>
+        <v>5.207160899370299</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0962902978619041</v>
+        <v>0.09613254665462653</v>
       </c>
       <c r="C28">
-        <v>50.86384649983155</v>
+        <v>50.43077196165465</v>
       </c>
       <c r="D28">
-        <v>64.10784649983155</v>
+        <v>64.30877196165466</v>
       </c>
       <c r="E28">
-        <v>-13.616</v>
+        <v>-12.982</v>
       </c>
       <c r="F28">
-        <v>16.484</v>
+        <v>17.118</v>
       </c>
       <c r="G28">
         <v>3.24</v>
@@ -3571,28 +3571,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M28">
-        <v>0.9115652000000001</v>
+        <v>0.9466254000000002</v>
       </c>
       <c r="N28">
-        <v>3.835101466666667</v>
+        <v>3.800041266666667</v>
       </c>
       <c r="O28">
-        <v>0.8820733373333335</v>
+        <v>0.8740094913333334</v>
       </c>
       <c r="P28">
-        <v>2.953028129333334</v>
+        <v>2.926031775333334</v>
       </c>
       <c r="Q28">
-        <v>5.773028129333333</v>
+        <v>5.746031775333334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1151611322458164</v>
+        <v>0.1159392830885295</v>
       </c>
       <c r="T28">
-        <v>1.07299465635934</v>
+        <v>1.085032402414488</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.207160899370299</v>
+        <v>5.014303088282509</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09613254665462653</v>
+        <v>0.09597479544734897</v>
       </c>
       <c r="C29">
-        <v>50.43077196165465</v>
+        <v>49.99896085599969</v>
       </c>
       <c r="D29">
-        <v>64.30877196165466</v>
+        <v>64.5109608559997</v>
       </c>
       <c r="E29">
-        <v>-12.982</v>
+        <v>-12.348</v>
       </c>
       <c r="F29">
-        <v>17.118</v>
+        <v>17.752</v>
       </c>
       <c r="G29">
         <v>3.24</v>
@@ -3653,28 +3653,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M29">
-        <v>0.9466254000000002</v>
+        <v>0.9816856000000002</v>
       </c>
       <c r="N29">
-        <v>3.800041266666667</v>
+        <v>3.764981066666667</v>
       </c>
       <c r="O29">
-        <v>0.8740094913333334</v>
+        <v>0.8659456453333334</v>
       </c>
       <c r="P29">
-        <v>2.926031775333334</v>
+        <v>2.899035421333334</v>
       </c>
       <c r="Q29">
-        <v>5.746031775333334</v>
+        <v>5.719035421333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1159392830885295</v>
+        <v>0.1167390492324291</v>
       </c>
       <c r="T29">
-        <v>1.085032402414488</v>
+        <v>1.097404530304502</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.014303088282509</v>
+        <v>4.835220835129563</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09597479544734897</v>
+        <v>0.09581704424007138</v>
       </c>
       <c r="C30">
-        <v>49.99896085599969</v>
+        <v>49.56842513727199</v>
       </c>
       <c r="D30">
-        <v>64.5109608559997</v>
+        <v>64.714425137272</v>
       </c>
       <c r="E30">
-        <v>-12.348</v>
+        <v>-11.714</v>
       </c>
       <c r="F30">
-        <v>17.752</v>
+        <v>18.386</v>
       </c>
       <c r="G30">
         <v>3.24</v>
@@ -3735,28 +3735,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M30">
-        <v>0.9816856000000002</v>
+        <v>1.0167458</v>
       </c>
       <c r="N30">
-        <v>3.764981066666667</v>
+        <v>3.729920866666667</v>
       </c>
       <c r="O30">
-        <v>0.8659456453333334</v>
+        <v>0.8578817993333334</v>
       </c>
       <c r="P30">
-        <v>2.899035421333334</v>
+        <v>2.872039067333334</v>
       </c>
       <c r="Q30">
-        <v>5.719035421333334</v>
+        <v>5.692039067333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1167390492324291</v>
+        <v>0.1175613440001005</v>
       </c>
       <c r="T30">
-        <v>1.097404530304502</v>
+        <v>1.110125168839305</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.835220835129563</v>
+        <v>4.668489082194061</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09581704424007138</v>
+        <v>0.0956592930327938</v>
       </c>
       <c r="C31">
-        <v>49.568425137272</v>
+        <v>49.13917691116828</v>
       </c>
       <c r="D31">
-        <v>64.714425137272</v>
+        <v>64.91917691116828</v>
       </c>
       <c r="E31">
-        <v>-11.714</v>
+        <v>-11.08</v>
       </c>
       <c r="F31">
-        <v>18.386</v>
+        <v>19.02</v>
       </c>
       <c r="G31">
         <v>3.24</v>
@@ -3817,28 +3817,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M31">
-        <v>1.0167458</v>
+        <v>1.051806</v>
       </c>
       <c r="N31">
-        <v>3.729920866666667</v>
+        <v>3.694860666666667</v>
       </c>
       <c r="O31">
-        <v>0.8578817993333335</v>
+        <v>0.8498179533333334</v>
       </c>
       <c r="P31">
-        <v>2.872039067333334</v>
+        <v>2.845042713333334</v>
       </c>
       <c r="Q31">
-        <v>5.692039067333334</v>
+        <v>5.665042713333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1175613440001005</v>
+        <v>0.1184071329039912</v>
       </c>
       <c r="T31">
-        <v>1.110125168839305</v>
+        <v>1.123209254189388</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.668489082194062</v>
+        <v>4.512872779454259</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0956592930327938</v>
+        <v>0.09609829182551621</v>
       </c>
       <c r="C32">
-        <v>49.13917691116828</v>
+        <v>47.93856839914567</v>
       </c>
       <c r="D32">
-        <v>64.91917691116828</v>
+        <v>64.35256839914567</v>
       </c>
       <c r="E32">
-        <v>-11.08</v>
+        <v>-10.446</v>
       </c>
       <c r="F32">
-        <v>19.02</v>
+        <v>19.654</v>
       </c>
       <c r="G32">
         <v>3.24</v>
@@ -3899,45 +3899,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M32">
-        <v>1.051806</v>
+        <v>1.1360012</v>
       </c>
       <c r="N32">
-        <v>3.694860666666667</v>
+        <v>3.610665466666667</v>
       </c>
       <c r="O32">
-        <v>0.8498179533333334</v>
+        <v>0.8304530573333335</v>
       </c>
       <c r="P32">
-        <v>2.845042713333334</v>
+        <v>2.780212409333334</v>
       </c>
       <c r="Q32">
-        <v>5.665042713333333</v>
+        <v>5.600212409333334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1184071329039912</v>
+        <v>0.1192774374282844</v>
       </c>
       <c r="T32">
-        <v>1.123209254189388</v>
+        <v>1.136672588390198</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.23</v>
       </c>
       <c r="W32">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.512872779454259</v>
+        <v>4.178399342066422</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09609829182551621</v>
+        <v>0.09595979061823864</v>
       </c>
       <c r="C33">
-        <v>47.93856839914567</v>
+        <v>47.48225870257076</v>
       </c>
       <c r="D33">
-        <v>64.35256839914567</v>
+        <v>64.53025870257076</v>
       </c>
       <c r="E33">
-        <v>-10.446</v>
+        <v>-9.812000000000001</v>
       </c>
       <c r="F33">
-        <v>19.654</v>
+        <v>20.288</v>
       </c>
       <c r="G33">
         <v>3.24</v>
@@ -3981,28 +3981,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M33">
-        <v>1.1360012</v>
+        <v>1.1726464</v>
       </c>
       <c r="N33">
-        <v>3.610665466666667</v>
+        <v>3.574020266666667</v>
       </c>
       <c r="O33">
-        <v>0.8304530573333335</v>
+        <v>0.8220246613333334</v>
       </c>
       <c r="P33">
-        <v>2.780212409333334</v>
+        <v>2.751995605333334</v>
       </c>
       <c r="Q33">
-        <v>5.600212409333334</v>
+        <v>5.571995605333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1192774374282844</v>
+        <v>0.1201733391444686</v>
       </c>
       <c r="T33">
-        <v>1.136672588390198</v>
+        <v>1.150531903008678</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.178399342066422</v>
+        <v>4.047824362626847</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09595979061823864</v>
+        <v>0.09671063941096106</v>
       </c>
       <c r="C34">
-        <v>47.48225870257076</v>
+        <v>45.89654276654073</v>
       </c>
       <c r="D34">
-        <v>64.53025870257076</v>
+        <v>63.57854276654073</v>
       </c>
       <c r="E34">
-        <v>-9.812000000000001</v>
+        <v>-9.178000000000001</v>
       </c>
       <c r="F34">
-        <v>20.288</v>
+        <v>20.922</v>
       </c>
       <c r="G34">
         <v>3.24</v>
@@ -4063,45 +4063,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M34">
-        <v>1.1726464</v>
+        <v>1.2825186</v>
       </c>
       <c r="N34">
-        <v>3.574020266666667</v>
+        <v>3.464148066666667</v>
       </c>
       <c r="O34">
-        <v>0.8220246613333334</v>
+        <v>0.7967540553333334</v>
       </c>
       <c r="P34">
-        <v>2.751995605333334</v>
+        <v>2.667394011333334</v>
       </c>
       <c r="Q34">
-        <v>5.571995605333334</v>
+        <v>5.487394011333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1201733391444686</v>
+        <v>0.1210959841954643</v>
       </c>
       <c r="T34">
-        <v>1.150531903008678</v>
+        <v>1.164804928511293</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.23</v>
       </c>
       <c r="W34">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.047824362626847</v>
+        <v>3.701050937324938</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09671063941096106</v>
+        <v>0.09659908820368349</v>
       </c>
       <c r="C35">
-        <v>45.89654276654073</v>
+        <v>45.40215675280204</v>
       </c>
       <c r="D35">
-        <v>63.57854276654073</v>
+        <v>63.71815675280204</v>
       </c>
       <c r="E35">
-        <v>-9.178000000000001</v>
+        <v>-8.544</v>
       </c>
       <c r="F35">
-        <v>20.922</v>
+        <v>21.556</v>
       </c>
       <c r="G35">
         <v>3.24</v>
@@ -4145,28 +4145,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M35">
-        <v>1.2825186</v>
+        <v>1.3213828</v>
       </c>
       <c r="N35">
-        <v>3.464148066666667</v>
+        <v>3.425283866666667</v>
       </c>
       <c r="O35">
-        <v>0.7967540553333334</v>
+        <v>0.7878152893333333</v>
       </c>
       <c r="P35">
-        <v>2.667394011333334</v>
+        <v>2.637468577333333</v>
       </c>
       <c r="Q35">
-        <v>5.487394011333334</v>
+        <v>5.457468577333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1210959841954643</v>
+        <v>0.1220465881873992</v>
       </c>
       <c r="T35">
-        <v>1.164804928511293</v>
+        <v>1.179510469938229</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.701050937324938</v>
+        <v>3.592196497991851</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09659908820368349</v>
+        <v>0.09724213699640591</v>
       </c>
       <c r="C36">
-        <v>45.40215675280204</v>
+        <v>43.97165244394625</v>
       </c>
       <c r="D36">
-        <v>63.71815675280204</v>
+        <v>62.92165244394625</v>
       </c>
       <c r="E36">
-        <v>-8.544</v>
+        <v>-7.91</v>
       </c>
       <c r="F36">
-        <v>21.556</v>
+        <v>22.19</v>
       </c>
       <c r="G36">
         <v>3.24</v>
@@ -4227,45 +4227,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M36">
-        <v>1.3213828</v>
+        <v>1.422379</v>
       </c>
       <c r="N36">
-        <v>3.425283866666667</v>
+        <v>3.324287666666667</v>
       </c>
       <c r="O36">
-        <v>0.7878152893333333</v>
+        <v>0.7645861633333334</v>
       </c>
       <c r="P36">
-        <v>2.637468577333333</v>
+        <v>2.559701503333333</v>
       </c>
       <c r="Q36">
-        <v>5.457468577333334</v>
+        <v>5.379701503333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1220465881873992</v>
+        <v>0.1230264415329322</v>
       </c>
       <c r="T36">
-        <v>1.179510469938229</v>
+        <v>1.194668489562917</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.23</v>
       </c>
       <c r="W36">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.592196497991851</v>
+        <v>3.33713213332499</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09724213699640591</v>
+        <v>0.09715214578912831</v>
       </c>
       <c r="C37">
-        <v>43.97165244394625</v>
+        <v>43.44791843926772</v>
       </c>
       <c r="D37">
-        <v>62.92165244394625</v>
+        <v>63.03191843926772</v>
       </c>
       <c r="E37">
-        <v>-7.91</v>
+        <v>-7.276</v>
       </c>
       <c r="F37">
-        <v>22.19</v>
+        <v>22.824</v>
       </c>
       <c r="G37">
         <v>3.24</v>
@@ -4309,28 +4309,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M37">
-        <v>1.422379</v>
+        <v>1.4630184</v>
       </c>
       <c r="N37">
-        <v>3.324287666666667</v>
+        <v>3.283648266666667</v>
       </c>
       <c r="O37">
-        <v>0.7645861633333334</v>
+        <v>0.7552391013333334</v>
       </c>
       <c r="P37">
-        <v>2.559701503333333</v>
+        <v>2.528409165333334</v>
       </c>
       <c r="Q37">
-        <v>5.379701503333333</v>
+        <v>5.348409165333334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1230264415329322</v>
+        <v>0.124036915295513</v>
       </c>
       <c r="T37">
-        <v>1.194668489562917</v>
+        <v>1.210300197300877</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.33713213332499</v>
+        <v>3.244434018510407</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09715214578912831</v>
+        <v>0.09706215458185075</v>
       </c>
       <c r="C38">
-        <v>43.44791843926772</v>
+        <v>42.92457158062787</v>
       </c>
       <c r="D38">
-        <v>63.03191843926772</v>
+        <v>63.14257158062787</v>
       </c>
       <c r="E38">
-        <v>-7.276000000000003</v>
+        <v>-6.642000000000003</v>
       </c>
       <c r="F38">
-        <v>22.824</v>
+        <v>23.458</v>
       </c>
       <c r="G38">
         <v>3.24</v>
@@ -4391,28 +4391,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M38">
-        <v>1.4630184</v>
+        <v>1.5036578</v>
       </c>
       <c r="N38">
-        <v>3.283648266666667</v>
+        <v>3.243008866666667</v>
       </c>
       <c r="O38">
-        <v>0.7552391013333334</v>
+        <v>0.7458920393333335</v>
       </c>
       <c r="P38">
-        <v>2.528409165333334</v>
+        <v>2.497116827333334</v>
       </c>
       <c r="Q38">
-        <v>5.348409165333334</v>
+        <v>5.317116827333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.124036915295513</v>
+        <v>0.1250794675902393</v>
       </c>
       <c r="T38">
-        <v>1.210300197300877</v>
+        <v>1.22642814972893</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.244434018510407</v>
+        <v>3.156746612604721</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09706215458185075</v>
+        <v>0.09697216337457318</v>
       </c>
       <c r="C39">
-        <v>42.92457158062787</v>
+        <v>42.40161391052816</v>
       </c>
       <c r="D39">
-        <v>63.14257158062787</v>
+        <v>63.25361391052815</v>
       </c>
       <c r="E39">
-        <v>-6.642000000000003</v>
+        <v>-6.008000000000003</v>
       </c>
       <c r="F39">
-        <v>23.458</v>
+        <v>24.092</v>
       </c>
       <c r="G39">
         <v>3.24</v>
@@ -4473,28 +4473,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M39">
-        <v>1.5036578</v>
+        <v>1.5442972</v>
       </c>
       <c r="N39">
-        <v>3.243008866666667</v>
+        <v>3.202369466666667</v>
       </c>
       <c r="O39">
-        <v>0.7458920393333335</v>
+        <v>0.7365449773333335</v>
       </c>
       <c r="P39">
-        <v>2.497116827333334</v>
+        <v>2.465824489333333</v>
       </c>
       <c r="Q39">
-        <v>5.317116827333334</v>
+        <v>5.285824489333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1250794675902393</v>
+        <v>0.1261556506041503</v>
       </c>
       <c r="T39">
-        <v>1.22642814972893</v>
+        <v>1.243076358686921</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.156746612604721</v>
+        <v>3.073674333325649</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09697216337457318</v>
+        <v>0.09922451216729559</v>
       </c>
       <c r="C40">
-        <v>42.40161391052816</v>
+        <v>39.10087545757656</v>
       </c>
       <c r="D40">
-        <v>63.25361391052815</v>
+        <v>60.58687545757655</v>
       </c>
       <c r="E40">
-        <v>-6.008000000000003</v>
+        <v>-5.374000000000002</v>
       </c>
       <c r="F40">
-        <v>24.092</v>
+        <v>24.726</v>
       </c>
       <c r="G40">
         <v>3.24</v>
@@ -4555,45 +4555,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M40">
-        <v>1.5442972</v>
+        <v>1.7777994</v>
       </c>
       <c r="N40">
-        <v>3.202369466666667</v>
+        <v>2.968867266666667</v>
       </c>
       <c r="O40">
-        <v>0.7365449773333335</v>
+        <v>0.6828394713333334</v>
       </c>
       <c r="P40">
-        <v>2.465824489333333</v>
+        <v>2.286027795333333</v>
       </c>
       <c r="Q40">
-        <v>5.285824489333334</v>
+        <v>5.106027795333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1261556506041503</v>
+        <v>0.127267118307042</v>
       </c>
       <c r="T40">
-        <v>1.243076358686921</v>
+        <v>1.260270410561567</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.23</v>
       </c>
       <c r="W40">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.073674333325649</v>
+        <v>2.669967526519959</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09922451216729559</v>
+        <v>0.09919458096001801</v>
       </c>
       <c r="C41">
-        <v>39.10087545757656</v>
+        <v>38.50083842338725</v>
       </c>
       <c r="D41">
-        <v>60.58687545757655</v>
+        <v>60.62083842338725</v>
       </c>
       <c r="E41">
-        <v>-5.374000000000002</v>
+        <v>-4.740000000000002</v>
       </c>
       <c r="F41">
-        <v>24.726</v>
+        <v>25.36</v>
       </c>
       <c r="G41">
         <v>3.24</v>
@@ -4637,28 +4637,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M41">
-        <v>1.7777994</v>
+        <v>1.823384</v>
       </c>
       <c r="N41">
-        <v>2.968867266666667</v>
+        <v>2.923282666666667</v>
       </c>
       <c r="O41">
-        <v>0.6828394713333334</v>
+        <v>0.6723550133333335</v>
       </c>
       <c r="P41">
-        <v>2.286027795333333</v>
+        <v>2.250927653333334</v>
       </c>
       <c r="Q41">
-        <v>5.106027795333334</v>
+        <v>5.070927653333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.127267118307042</v>
+        <v>0.1284156349333634</v>
       </c>
       <c r="T41">
-        <v>1.260270410561567</v>
+        <v>1.278037597498702</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.669967526519959</v>
+        <v>2.60321833835696</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09919458096001801</v>
+        <v>0.09916464975274043</v>
       </c>
       <c r="C42">
-        <v>38.50083842338725</v>
+        <v>37.90083948754861</v>
       </c>
       <c r="D42">
-        <v>60.62083842338725</v>
+        <v>60.65483948754861</v>
       </c>
       <c r="E42">
-        <v>-4.740000000000002</v>
+        <v>-4.106000000000002</v>
       </c>
       <c r="F42">
-        <v>25.36</v>
+        <v>25.994</v>
       </c>
       <c r="G42">
         <v>3.24</v>
@@ -4719,28 +4719,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M42">
-        <v>1.823384</v>
+        <v>1.8689686</v>
       </c>
       <c r="N42">
-        <v>2.923282666666667</v>
+        <v>2.877698066666667</v>
       </c>
       <c r="O42">
-        <v>0.6723550133333335</v>
+        <v>0.6618705553333334</v>
       </c>
       <c r="P42">
-        <v>2.250927653333334</v>
+        <v>2.215827511333333</v>
       </c>
       <c r="Q42">
-        <v>5.070927653333333</v>
+        <v>5.035827511333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1284156349333634</v>
+        <v>0.1296030843266787</v>
       </c>
       <c r="T42">
-        <v>1.278037597498702</v>
+        <v>1.296407061959129</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.60321833835696</v>
+        <v>2.539725208153132</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09916464975274043</v>
+        <v>0.1003959785454629</v>
       </c>
       <c r="C43">
-        <v>37.90083948754861</v>
+        <v>35.89886235317444</v>
       </c>
       <c r="D43">
-        <v>60.65483948754861</v>
+        <v>59.28686235317444</v>
       </c>
       <c r="E43">
-        <v>-4.106000000000002</v>
+        <v>-3.471999999999998</v>
       </c>
       <c r="F43">
-        <v>25.994</v>
+        <v>26.628</v>
       </c>
       <c r="G43">
         <v>3.24</v>
@@ -4801,45 +4801,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M43">
-        <v>1.8689686</v>
+        <v>2.0184024</v>
       </c>
       <c r="N43">
-        <v>2.877698066666667</v>
+        <v>2.728264266666667</v>
       </c>
       <c r="O43">
-        <v>0.6618705553333334</v>
+        <v>0.6275007813333334</v>
       </c>
       <c r="P43">
-        <v>2.215827511333333</v>
+        <v>2.100763485333333</v>
       </c>
       <c r="Q43">
-        <v>5.035827511333334</v>
+        <v>4.920763485333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1296030843266787</v>
+        <v>0.130831480250798</v>
       </c>
       <c r="T43">
-        <v>1.296407061959129</v>
+        <v>1.315409956228536</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.23</v>
       </c>
       <c r="W43">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.539725208153132</v>
+        <v>2.351694918053341</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1003959785454629</v>
+        <v>0.1003960773381853</v>
       </c>
       <c r="C44">
-        <v>35.89886235317444</v>
+        <v>35.26475507238026</v>
       </c>
       <c r="D44">
-        <v>59.28686235317443</v>
+        <v>59.28675507238026</v>
       </c>
       <c r="E44">
-        <v>-3.472000000000001</v>
+        <v>-2.838000000000001</v>
       </c>
       <c r="F44">
-        <v>26.628</v>
+        <v>27.262</v>
       </c>
       <c r="G44">
         <v>3.24</v>
@@ -4883,28 +4883,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M44">
-        <v>2.0184024</v>
+        <v>2.0664596</v>
       </c>
       <c r="N44">
-        <v>2.728264266666667</v>
+        <v>2.680207066666667</v>
       </c>
       <c r="O44">
-        <v>0.6275007813333334</v>
+        <v>0.6164476253333333</v>
       </c>
       <c r="P44">
-        <v>2.100763485333333</v>
+        <v>2.063759441333334</v>
       </c>
       <c r="Q44">
-        <v>4.920763485333334</v>
+        <v>4.883759441333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.130831480250798</v>
+        <v>0.13210297778629</v>
       </c>
       <c r="T44">
-        <v>1.315409956228536</v>
+        <v>1.335079618717923</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.351694918053341</v>
+        <v>2.297004338563728</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1003960773381853</v>
+        <v>0.1003961761309077</v>
       </c>
       <c r="C45">
-        <v>35.26475507238026</v>
+        <v>34.63064779197435</v>
       </c>
       <c r="D45">
-        <v>59.28675507238026</v>
+        <v>59.28664779197435</v>
       </c>
       <c r="E45">
-        <v>-2.838000000000001</v>
+        <v>-2.204000000000001</v>
       </c>
       <c r="F45">
-        <v>27.262</v>
+        <v>27.896</v>
       </c>
       <c r="G45">
         <v>3.24</v>
@@ -4965,28 +4965,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M45">
-        <v>2.0664596</v>
+        <v>2.1145168</v>
       </c>
       <c r="N45">
-        <v>2.680207066666667</v>
+        <v>2.632149866666667</v>
       </c>
       <c r="O45">
-        <v>0.6164476253333333</v>
+        <v>0.6053944693333334</v>
       </c>
       <c r="P45">
-        <v>2.063759441333334</v>
+        <v>2.026755397333333</v>
       </c>
       <c r="Q45">
-        <v>4.883759441333334</v>
+        <v>4.846755397333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.13210297778629</v>
+        <v>0.1334198859480494</v>
       </c>
       <c r="T45">
-        <v>1.335079618717923</v>
+        <v>1.355451769153359</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.297004338563728</v>
+        <v>2.244799694505462</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1003961761309077</v>
+        <v>0.1003962749236301</v>
       </c>
       <c r="C46">
-        <v>34.63064779197435</v>
+        <v>33.99654051195667</v>
       </c>
       <c r="D46">
-        <v>59.28664779197435</v>
+        <v>59.28654051195667</v>
       </c>
       <c r="E46">
-        <v>-2.204000000000001</v>
+        <v>-1.57</v>
       </c>
       <c r="F46">
-        <v>27.896</v>
+        <v>28.53</v>
       </c>
       <c r="G46">
         <v>3.24</v>
@@ -5047,28 +5047,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M46">
-        <v>2.1145168</v>
+        <v>2.162574</v>
       </c>
       <c r="N46">
-        <v>2.632149866666667</v>
+        <v>2.584092666666667</v>
       </c>
       <c r="O46">
-        <v>0.6053944693333334</v>
+        <v>0.5943413133333334</v>
       </c>
       <c r="P46">
-        <v>2.026755397333333</v>
+        <v>1.989751353333333</v>
       </c>
       <c r="Q46">
-        <v>4.846755397333334</v>
+        <v>4.809751353333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1334198859480494</v>
+        <v>0.1347846816793275</v>
       </c>
       <c r="T46">
-        <v>1.355451769153359</v>
+        <v>1.376564725059174</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.244799694505462</v>
+        <v>2.194915256849785</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1003962749236301</v>
+        <v>0.1003963737163525</v>
       </c>
       <c r="C47">
-        <v>33.99654051195667</v>
+        <v>33.36243323232725</v>
       </c>
       <c r="D47">
-        <v>59.28654051195667</v>
+        <v>59.28643323232725</v>
       </c>
       <c r="E47">
-        <v>-1.57</v>
+        <v>-0.9359999999999999</v>
       </c>
       <c r="F47">
-        <v>28.53</v>
+        <v>29.164</v>
       </c>
       <c r="G47">
         <v>3.24</v>
@@ -5129,28 +5129,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M47">
-        <v>2.162574</v>
+        <v>2.2106312</v>
       </c>
       <c r="N47">
-        <v>2.584092666666667</v>
+        <v>2.536035466666667</v>
       </c>
       <c r="O47">
-        <v>0.5943413133333334</v>
+        <v>0.5832881573333334</v>
       </c>
       <c r="P47">
-        <v>1.989751353333333</v>
+        <v>1.952747309333333</v>
       </c>
       <c r="Q47">
-        <v>4.809751353333334</v>
+        <v>4.772747309333333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1347846816793275</v>
+        <v>0.1362000254006528</v>
       </c>
       <c r="T47">
-        <v>1.376564725059174</v>
+        <v>1.398459642294835</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.194915256849785</v>
+        <v>2.147199707787833</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1003963737163525</v>
+        <v>0.1003964725090749</v>
       </c>
       <c r="C48">
-        <v>33.36243323232725</v>
+        <v>32.72832595308608</v>
       </c>
       <c r="D48">
-        <v>59.28643323232725</v>
+        <v>59.28632595308608</v>
       </c>
       <c r="E48">
-        <v>-0.9359999999999999</v>
+        <v>-0.3019999999999996</v>
       </c>
       <c r="F48">
-        <v>29.164</v>
+        <v>29.798</v>
       </c>
       <c r="G48">
         <v>3.24</v>
@@ -5211,28 +5211,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M48">
-        <v>2.2106312</v>
+        <v>2.2586884</v>
       </c>
       <c r="N48">
-        <v>2.536035466666667</v>
+        <v>2.487978266666667</v>
       </c>
       <c r="O48">
-        <v>0.5832881573333334</v>
+        <v>0.5722350013333334</v>
       </c>
       <c r="P48">
-        <v>1.952747309333333</v>
+        <v>1.915743265333333</v>
       </c>
       <c r="Q48">
-        <v>4.772747309333333</v>
+        <v>4.735743265333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1362000254006528</v>
+        <v>0.1376687783190093</v>
       </c>
       <c r="T48">
-        <v>1.398459642294835</v>
+        <v>1.421180782822407</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.147199707787833</v>
+        <v>2.101514607622134</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1003964725090749</v>
+        <v>0.1003965713017974</v>
       </c>
       <c r="C49">
-        <v>32.72832595308608</v>
+        <v>32.09421867423315</v>
       </c>
       <c r="D49">
-        <v>59.28632595308608</v>
+        <v>59.28621867423315</v>
       </c>
       <c r="E49">
-        <v>-0.3019999999999996</v>
+        <v>0.3320000000000007</v>
       </c>
       <c r="F49">
-        <v>29.798</v>
+        <v>30.432</v>
       </c>
       <c r="G49">
         <v>3.24</v>
@@ -5293,28 +5293,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M49">
-        <v>2.2586884</v>
+        <v>2.3067456</v>
       </c>
       <c r="N49">
-        <v>2.487978266666667</v>
+        <v>2.439921066666667</v>
       </c>
       <c r="O49">
-        <v>0.5722350013333334</v>
+        <v>0.5611818453333334</v>
       </c>
       <c r="P49">
-        <v>1.915743265333333</v>
+        <v>1.878739221333333</v>
       </c>
       <c r="Q49">
-        <v>4.735743265333333</v>
+        <v>4.698739221333334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1376687783190093</v>
+        <v>0.1391940217342257</v>
       </c>
       <c r="T49">
-        <v>1.421180782822407</v>
+        <v>1.444775813370271</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.101514607622134</v>
+        <v>2.057733053296674</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1003965713017974</v>
+        <v>0.1003966700945198</v>
       </c>
       <c r="C50">
-        <v>32.09421867423315</v>
+        <v>31.46011139576846</v>
       </c>
       <c r="D50">
-        <v>59.28621867423315</v>
+        <v>59.28611139576846</v>
       </c>
       <c r="E50">
-        <v>0.3319999999999972</v>
+        <v>0.9659999999999975</v>
       </c>
       <c r="F50">
-        <v>30.432</v>
+        <v>31.066</v>
       </c>
       <c r="G50">
         <v>3.24</v>
@@ -5375,28 +5375,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M50">
-        <v>2.3067456</v>
+        <v>2.3548028</v>
       </c>
       <c r="N50">
-        <v>2.439921066666667</v>
+        <v>2.391863866666667</v>
       </c>
       <c r="O50">
-        <v>0.5611818453333334</v>
+        <v>0.5501286893333334</v>
       </c>
       <c r="P50">
-        <v>1.878739221333333</v>
+        <v>1.841735177333333</v>
       </c>
       <c r="Q50">
-        <v>4.698739221333334</v>
+        <v>4.661735177333334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1391940217342257</v>
+        <v>0.1407790786167055</v>
       </c>
       <c r="T50">
-        <v>1.444775813370271</v>
+        <v>1.469296139233737</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.057733053296674</v>
+        <v>2.015738501188578</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1003966700945198</v>
+        <v>0.1058637688872422</v>
       </c>
       <c r="C51">
-        <v>31.46011139576846</v>
+        <v>25.42979621205948</v>
       </c>
       <c r="D51">
-        <v>59.28611139576846</v>
+        <v>53.88979621205947</v>
       </c>
       <c r="E51">
-        <v>0.9659999999999975</v>
+        <v>1.599999999999998</v>
       </c>
       <c r="F51">
-        <v>31.066</v>
+        <v>31.7</v>
       </c>
       <c r="G51">
         <v>3.24</v>
@@ -5457,45 +5457,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M51">
-        <v>2.3548028</v>
+        <v>2.853</v>
       </c>
       <c r="N51">
-        <v>2.391863866666667</v>
+        <v>1.893666666666667</v>
       </c>
       <c r="O51">
-        <v>0.5501286893333334</v>
+        <v>0.4355433333333335</v>
       </c>
       <c r="P51">
-        <v>1.841735177333333</v>
+        <v>1.458123333333334</v>
       </c>
       <c r="Q51">
-        <v>4.661735177333334</v>
+        <v>4.278123333333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1407790786167055</v>
+        <v>0.1424275377744844</v>
       </c>
       <c r="T51">
-        <v>1.469296139233737</v>
+        <v>1.494797278131742</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.23</v>
       </c>
       <c r="W51">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.015738501188578</v>
+        <v>1.663745764692137</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1058637688872422</v>
+        <v>0.1059732076799647</v>
       </c>
       <c r="C52">
-        <v>25.42979621205948</v>
+        <v>24.69778524563613</v>
       </c>
       <c r="D52">
-        <v>53.88979621205947</v>
+        <v>53.79178524563613</v>
       </c>
       <c r="E52">
-        <v>1.599999999999998</v>
+        <v>2.234000000000002</v>
       </c>
       <c r="F52">
-        <v>31.7</v>
+        <v>32.334</v>
       </c>
       <c r="G52">
         <v>3.24</v>
@@ -5539,28 +5539,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M52">
-        <v>2.853</v>
+        <v>2.91006</v>
       </c>
       <c r="N52">
-        <v>1.893666666666667</v>
+        <v>1.836606666666667</v>
       </c>
       <c r="O52">
-        <v>0.4355433333333335</v>
+        <v>0.4224195333333334</v>
       </c>
       <c r="P52">
-        <v>1.458123333333334</v>
+        <v>1.414187133333334</v>
       </c>
       <c r="Q52">
-        <v>4.278123333333334</v>
+        <v>4.234187133333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1424275377744844</v>
+        <v>0.1441432809795197</v>
       </c>
       <c r="T52">
-        <v>1.494797278131742</v>
+        <v>1.52133927984191</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.663745764692137</v>
+        <v>1.631123298717781</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1059732076799647</v>
+        <v>0.1060826464726871</v>
       </c>
       <c r="C53">
-        <v>24.69778524563613</v>
+        <v>23.96613014288059</v>
       </c>
       <c r="D53">
-        <v>53.79178524563613</v>
+        <v>53.69413014288059</v>
       </c>
       <c r="E53">
-        <v>2.234000000000002</v>
+        <v>2.868000000000002</v>
       </c>
       <c r="F53">
-        <v>32.334</v>
+        <v>32.968</v>
       </c>
       <c r="G53">
         <v>3.24</v>
@@ -5621,28 +5621,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M53">
-        <v>2.91006</v>
+        <v>2.96712</v>
       </c>
       <c r="N53">
-        <v>1.836606666666667</v>
+        <v>1.779546666666667</v>
       </c>
       <c r="O53">
-        <v>0.4224195333333334</v>
+        <v>0.4092957333333334</v>
       </c>
       <c r="P53">
-        <v>1.414187133333334</v>
+        <v>1.370250933333333</v>
       </c>
       <c r="Q53">
-        <v>4.234187133333334</v>
+        <v>4.190250933333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1441432809795197</v>
+        <v>0.1459305134847647</v>
       </c>
       <c r="T53">
-        <v>1.52133927984191</v>
+        <v>1.548987198290002</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.631123298717781</v>
+        <v>1.599755542973208</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1060826464726871</v>
+        <v>0.1061920852654095</v>
       </c>
       <c r="C54">
-        <v>23.96613014288059</v>
+        <v>23.23482896917061</v>
       </c>
       <c r="D54">
-        <v>53.69413014288059</v>
+        <v>53.59682896917062</v>
       </c>
       <c r="E54">
-        <v>2.868000000000002</v>
+        <v>3.502000000000002</v>
       </c>
       <c r="F54">
-        <v>32.968</v>
+        <v>33.602</v>
       </c>
       <c r="G54">
         <v>3.24</v>
@@ -5703,28 +5703,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M54">
-        <v>2.96712</v>
+        <v>3.02418</v>
       </c>
       <c r="N54">
-        <v>1.779546666666667</v>
+        <v>1.722486666666667</v>
       </c>
       <c r="O54">
-        <v>0.4092957333333334</v>
+        <v>0.3961719333333333</v>
       </c>
       <c r="P54">
-        <v>1.370250933333333</v>
+        <v>1.326314733333333</v>
       </c>
       <c r="Q54">
-        <v>4.190250933333333</v>
+        <v>4.146314733333334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1459305134847647</v>
+        <v>0.1477937984370415</v>
       </c>
       <c r="T54">
-        <v>1.548987198290002</v>
+        <v>1.577811623906097</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.599755542973208</v>
+        <v>1.569571476124657</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1061920852654095</v>
+        <v>0.1063015240581319</v>
       </c>
       <c r="C55">
-        <v>23.23482896917061</v>
+        <v>22.50387980388183</v>
       </c>
       <c r="D55">
-        <v>53.59682896917062</v>
+        <v>53.49987980388183</v>
       </c>
       <c r="E55">
-        <v>3.502000000000002</v>
+        <v>4.136000000000003</v>
       </c>
       <c r="F55">
-        <v>33.602</v>
+        <v>34.236</v>
       </c>
       <c r="G55">
         <v>3.24</v>
@@ -5785,28 +5785,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M55">
-        <v>3.02418</v>
+        <v>3.08124</v>
       </c>
       <c r="N55">
-        <v>1.722486666666667</v>
+        <v>1.665426666666667</v>
       </c>
       <c r="O55">
-        <v>0.3961719333333333</v>
+        <v>0.3830481333333334</v>
       </c>
       <c r="P55">
-        <v>1.326314733333333</v>
+        <v>1.282378533333334</v>
       </c>
       <c r="Q55">
-        <v>4.146314733333334</v>
+        <v>4.102378533333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1477937984370415</v>
+        <v>0.1497380957785476</v>
       </c>
       <c r="T55">
-        <v>1.577811623906097</v>
+        <v>1.607889285418545</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.569571476124657</v>
+        <v>1.540505337677905</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1063015240581319</v>
+        <v>0.1064109628508543</v>
       </c>
       <c r="C56">
-        <v>22.50387980388183</v>
+        <v>21.77328074026128</v>
       </c>
       <c r="D56">
-        <v>53.49987980388183</v>
+        <v>53.40328074026129</v>
       </c>
       <c r="E56">
-        <v>4.136000000000003</v>
+        <v>4.770000000000003</v>
       </c>
       <c r="F56">
-        <v>34.236</v>
+        <v>34.87</v>
       </c>
       <c r="G56">
         <v>3.24</v>
@@ -5867,28 +5867,28 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M56">
-        <v>3.08124</v>
+        <v>3.1383</v>
       </c>
       <c r="N56">
-        <v>1.665426666666667</v>
+        <v>1.608366666666667</v>
       </c>
       <c r="O56">
-        <v>0.3830481333333334</v>
+        <v>0.3699243333333334</v>
       </c>
       <c r="P56">
-        <v>1.282378533333334</v>
+        <v>1.238442333333333</v>
       </c>
       <c r="Q56">
-        <v>4.102378533333334</v>
+        <v>4.058442333333334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1497380957785476</v>
+        <v>0.1517688063352318</v>
       </c>
       <c r="T56">
-        <v>1.607889285418545</v>
+        <v>1.639303731887102</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.540505337677905</v>
+        <v>1.512496149720125</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1064109628508543</v>
+        <v>0.1333283911677588</v>
       </c>
       <c r="C57">
-        <v>21.77328074026128</v>
+        <v>4.716278306017934</v>
       </c>
       <c r="D57">
-        <v>53.40328074026129</v>
+        <v>36.98027830601794</v>
       </c>
       <c r="E57">
-        <v>4.770000000000003</v>
+        <v>5.404000000000003</v>
       </c>
       <c r="F57">
-        <v>34.87</v>
+        <v>35.504</v>
       </c>
       <c r="G57">
         <v>3.24</v>
@@ -5949,45 +5949,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M57">
-        <v>3.1383</v>
+        <v>5.211987200000001</v>
       </c>
       <c r="N57">
-        <v>1.608366666666667</v>
+        <v>-0.4653205333333341</v>
       </c>
       <c r="O57">
-        <v>0.3699243333333334</v>
+        <v>-0.1070237226666668</v>
       </c>
       <c r="P57">
-        <v>1.238442333333333</v>
+        <v>-0.3582968106666673</v>
       </c>
       <c r="Q57">
-        <v>4.058442333333334</v>
+        <v>2.461703189333333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1517688063352318</v>
+        <v>0.1553185450734599</v>
       </c>
       <c r="T57">
-        <v>1.639303731887102</v>
+        <v>1.694217061215289</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.23</v>
+        <v>0.2094658508242946</v>
       </c>
       <c r="W57">
-        <v>0.0693</v>
+        <v>0.1160504130989936</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.512496149720125</v>
+        <v>0.9107210905404115</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1333283911677588</v>
+        <v>0.1343383911677588</v>
       </c>
       <c r="C58">
-        <v>4.716278306017934</v>
+        <v>3.660426490139457</v>
       </c>
       <c r="D58">
-        <v>36.98027830601794</v>
+        <v>36.55842649013946</v>
       </c>
       <c r="E58">
-        <v>5.404000000000003</v>
+        <v>6.038000000000004</v>
       </c>
       <c r="F58">
-        <v>35.504</v>
+        <v>36.13800000000001</v>
       </c>
       <c r="G58">
         <v>3.24</v>
@@ -6031,37 +6031,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M58">
-        <v>5.211987200000001</v>
+        <v>5.305058400000001</v>
       </c>
       <c r="N58">
-        <v>-0.4653205333333341</v>
+        <v>-0.5583917333333339</v>
       </c>
       <c r="O58">
-        <v>-0.1070237226666668</v>
+        <v>-0.1284300986666668</v>
       </c>
       <c r="P58">
-        <v>-0.3582968106666673</v>
+        <v>-0.4299616346666671</v>
       </c>
       <c r="Q58">
-        <v>2.461703189333333</v>
+        <v>2.390038365333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1553185450734599</v>
+        <v>0.157865487982145</v>
       </c>
       <c r="T58">
-        <v>1.694217061215289</v>
+        <v>1.733617457987737</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2094658508242946</v>
+        <v>0.2057910113361492</v>
       </c>
       <c r="W58">
-        <v>0.1160504130989936</v>
+        <v>0.1165898795358533</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9107210905404115</v>
+        <v>0.8947435275484745</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1343383911677588</v>
+        <v>0.1353483911677588</v>
       </c>
       <c r="C59">
-        <v>3.660426490139457</v>
+        <v>2.614090653911326</v>
       </c>
       <c r="D59">
-        <v>36.55842649013946</v>
+        <v>36.14609065391133</v>
       </c>
       <c r="E59">
-        <v>6.038000000000004</v>
+        <v>6.672000000000004</v>
       </c>
       <c r="F59">
-        <v>36.13800000000001</v>
+        <v>36.77200000000001</v>
       </c>
       <c r="G59">
         <v>3.24</v>
@@ -6113,37 +6113,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M59">
-        <v>5.305058400000001</v>
+        <v>5.398129600000002</v>
       </c>
       <c r="N59">
-        <v>-0.5583917333333339</v>
+        <v>-0.6514629333333346</v>
       </c>
       <c r="O59">
-        <v>-0.1284300986666668</v>
+        <v>-0.149836474666667</v>
       </c>
       <c r="P59">
-        <v>-0.4299616346666671</v>
+        <v>-0.5016264586666677</v>
       </c>
       <c r="Q59">
-        <v>2.390038365333333</v>
+        <v>2.318373541333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.157865487982145</v>
+        <v>0.1605337138864818</v>
       </c>
       <c r="T59">
-        <v>1.733617457987737</v>
+        <v>1.774894064130303</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2057910113361492</v>
+        <v>0.2022428904510431</v>
       </c>
       <c r="W59">
-        <v>0.1165898795358533</v>
+        <v>0.1171107436817869</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8947435275484745</v>
+        <v>0.8793169150045352</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1353483911677588</v>
+        <v>0.1363583911677587</v>
       </c>
       <c r="C60">
-        <v>2.614090653911333</v>
+        <v>1.576952401456964</v>
       </c>
       <c r="D60">
-        <v>36.14609065391133</v>
+        <v>35.74295240145696</v>
       </c>
       <c r="E60">
-        <v>6.671999999999997</v>
+        <v>7.305999999999997</v>
       </c>
       <c r="F60">
-        <v>36.772</v>
+        <v>37.406</v>
       </c>
       <c r="G60">
         <v>3.24</v>
@@ -6195,37 +6195,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M60">
-        <v>5.3981296</v>
+        <v>5.491200800000001</v>
       </c>
       <c r="N60">
-        <v>-0.6514629333333328</v>
+        <v>-0.7445341333333335</v>
       </c>
       <c r="O60">
-        <v>-0.1498364746666666</v>
+        <v>-0.1712428506666667</v>
       </c>
       <c r="P60">
-        <v>-0.5016264586666663</v>
+        <v>-0.5732912826666667</v>
       </c>
       <c r="Q60">
-        <v>2.318373541333334</v>
+        <v>2.246708717333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1605337138864818</v>
+        <v>0.1633320971520058</v>
       </c>
       <c r="T60">
-        <v>1.774894064130302</v>
+        <v>1.818184163255432</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2022428904510432</v>
+        <v>0.198815044850178</v>
       </c>
       <c r="W60">
-        <v>0.1171107436817869</v>
+        <v>0.1176139514159939</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8793169150045355</v>
+        <v>0.8644132384790348</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1363583911677587</v>
+        <v>0.1373683911677587</v>
       </c>
       <c r="C61">
-        <v>1.576952401456964</v>
+        <v>0.5487073845347723</v>
       </c>
       <c r="D61">
-        <v>35.74295240145696</v>
+        <v>35.34870738453477</v>
       </c>
       <c r="E61">
-        <v>7.305999999999997</v>
+        <v>7.939999999999998</v>
       </c>
       <c r="F61">
-        <v>37.406</v>
+        <v>38.04</v>
       </c>
       <c r="G61">
         <v>3.24</v>
@@ -6277,37 +6277,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M61">
-        <v>5.491200800000001</v>
+        <v>5.584272</v>
       </c>
       <c r="N61">
-        <v>-0.7445341333333335</v>
+        <v>-0.8376053333333333</v>
       </c>
       <c r="O61">
-        <v>-0.1712428506666667</v>
+        <v>-0.1926492266666667</v>
       </c>
       <c r="P61">
-        <v>-0.5732912826666667</v>
+        <v>-0.6449561066666667</v>
       </c>
       <c r="Q61">
-        <v>2.246708717333334</v>
+        <v>2.175043893333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1633320971520058</v>
+        <v>0.1662703995808059</v>
       </c>
       <c r="T61">
-        <v>1.818184163255432</v>
+        <v>1.863638767336817</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.198815044850178</v>
+        <v>0.1955014607693417</v>
       </c>
       <c r="W61">
-        <v>0.1176139514159939</v>
+        <v>0.1181003855590606</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8644132384790348</v>
+        <v>0.8500063511710509</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1373683911677587</v>
+        <v>0.1383783911677587</v>
       </c>
       <c r="C62">
-        <v>0.5487073845347723</v>
+        <v>-0.4709354637372982</v>
       </c>
       <c r="D62">
-        <v>35.34870738453477</v>
+        <v>34.9630645362627</v>
       </c>
       <c r="E62">
-        <v>7.939999999999998</v>
+        <v>8.573999999999998</v>
       </c>
       <c r="F62">
-        <v>38.04</v>
+        <v>38.674</v>
       </c>
       <c r="G62">
         <v>3.24</v>
@@ -6359,37 +6359,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M62">
-        <v>5.584272</v>
+        <v>5.6773432</v>
       </c>
       <c r="N62">
-        <v>-0.8376053333333333</v>
+        <v>-0.9306765333333331</v>
       </c>
       <c r="O62">
-        <v>-0.1926492266666667</v>
+        <v>-0.2140556026666666</v>
       </c>
       <c r="P62">
-        <v>-0.6449561066666667</v>
+        <v>-0.7166209306666664</v>
       </c>
       <c r="Q62">
-        <v>2.175043893333334</v>
+        <v>2.103379069333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1662703995808059</v>
+        <v>0.1693593841854419</v>
       </c>
       <c r="T62">
-        <v>1.863638767336817</v>
+        <v>1.91142437675571</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1955014607693417</v>
+        <v>0.1922965187895165</v>
       </c>
       <c r="W62">
-        <v>0.1181003855590606</v>
+        <v>0.118570871041699</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8500063511710509</v>
+        <v>0.8360718208239846</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1383783911677587</v>
+        <v>0.1393883911677588</v>
       </c>
       <c r="C63">
-        <v>-0.4709354637372982</v>
+        <v>-1.482254645539747</v>
       </c>
       <c r="D63">
-        <v>34.9630645362627</v>
+        <v>34.58574535446025</v>
       </c>
       <c r="E63">
-        <v>8.573999999999998</v>
+        <v>9.207999999999998</v>
       </c>
       <c r="F63">
-        <v>38.674</v>
+        <v>39.308</v>
       </c>
       <c r="G63">
         <v>3.24</v>
@@ -6441,37 +6441,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M63">
-        <v>5.6773432</v>
+        <v>5.770414400000001</v>
       </c>
       <c r="N63">
-        <v>-0.9306765333333331</v>
+        <v>-1.023747733333334</v>
       </c>
       <c r="O63">
-        <v>-0.2140556026666666</v>
+        <v>-0.2354619786666668</v>
       </c>
       <c r="P63">
-        <v>-0.7166209306666664</v>
+        <v>-0.7882857546666671</v>
       </c>
       <c r="Q63">
-        <v>2.103379069333334</v>
+        <v>2.031714245333333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1693593841854419</v>
+        <v>0.1726109469271641</v>
       </c>
       <c r="T63">
-        <v>1.91142437675571</v>
+        <v>1.961725018249281</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1922965187895165</v>
+        <v>0.1891949620348468</v>
       </c>
       <c r="W63">
-        <v>0.118570871041699</v>
+        <v>0.1190261795732845</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8360718208239846</v>
+        <v>0.8225867914558557</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1393883911677588</v>
+        <v>0.1403983911677588</v>
       </c>
       <c r="C64">
-        <v>-1.482254645539747</v>
+        <v>-2.485516769100158</v>
       </c>
       <c r="D64">
-        <v>34.58574535446025</v>
+        <v>34.21648323089984</v>
       </c>
       <c r="E64">
-        <v>9.207999999999998</v>
+        <v>9.841999999999999</v>
       </c>
       <c r="F64">
-        <v>39.308</v>
+        <v>39.942</v>
       </c>
       <c r="G64">
         <v>3.24</v>
@@ -6523,37 +6523,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M64">
-        <v>5.770414400000001</v>
+        <v>5.863485600000001</v>
       </c>
       <c r="N64">
-        <v>-1.023747733333334</v>
+        <v>-1.116818933333334</v>
       </c>
       <c r="O64">
-        <v>-0.2354619786666668</v>
+        <v>-0.2568683546666667</v>
       </c>
       <c r="P64">
-        <v>-0.7882857546666671</v>
+        <v>-0.8599505786666668</v>
       </c>
       <c r="Q64">
-        <v>2.031714245333333</v>
+        <v>1.960049421333333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1726109469271641</v>
+        <v>0.1760382698170875</v>
       </c>
       <c r="T64">
-        <v>1.961725018249281</v>
+        <v>2.0147446133371</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1891949620348468</v>
+        <v>0.1861918673993731</v>
       </c>
       <c r="W64">
-        <v>0.1190261795732845</v>
+        <v>0.119467033865772</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8225867914558557</v>
+        <v>0.8095298582581436</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1403983911677588</v>
+        <v>0.1776904935014995</v>
       </c>
       <c r="C65">
-        <v>-2.485516769100158</v>
+        <v>-12.79424434249371</v>
       </c>
       <c r="D65">
-        <v>34.21648323089984</v>
+        <v>24.54175565750629</v>
       </c>
       <c r="E65">
-        <v>9.841999999999999</v>
+        <v>10.476</v>
       </c>
       <c r="F65">
-        <v>39.942</v>
+        <v>40.576</v>
       </c>
       <c r="G65">
         <v>3.24</v>
@@ -6605,45 +6605,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M65">
-        <v>5.863485600000001</v>
+        <v>8.147660800000001</v>
       </c>
       <c r="N65">
-        <v>-1.116818933333334</v>
+        <v>-3.400994133333334</v>
       </c>
       <c r="O65">
-        <v>-0.2568683546666667</v>
+        <v>-0.7822286506666668</v>
       </c>
       <c r="P65">
-        <v>-0.8599505786666668</v>
+        <v>-2.618765482666667</v>
       </c>
       <c r="Q65">
-        <v>1.960049421333333</v>
+        <v>0.2012345173333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1760382698170875</v>
+        <v>0.184439617127953</v>
       </c>
       <c r="T65">
-        <v>2.0147446133371</v>
+        <v>2.144710784287565</v>
       </c>
       <c r="U65">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1861918673993731</v>
+        <v>0.1339934688166367</v>
       </c>
       <c r="W65">
-        <v>0.119467033865772</v>
+        <v>0.1738941114616194</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8095298582581436</v>
+        <v>0.5825802992027683</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1776904935014995</v>
+        <v>0.1792404935014995</v>
       </c>
       <c r="C66">
-        <v>-12.79424434249371</v>
+        <v>-13.71331314185863</v>
       </c>
       <c r="D66">
-        <v>24.54175565750629</v>
+        <v>24.25668685814137</v>
       </c>
       <c r="E66">
-        <v>10.476</v>
+        <v>11.11</v>
       </c>
       <c r="F66">
-        <v>40.576</v>
+        <v>41.21</v>
       </c>
       <c r="G66">
         <v>3.24</v>
@@ -6687,37 +6687,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M66">
-        <v>8.147660800000001</v>
+        <v>8.274968000000001</v>
       </c>
       <c r="N66">
-        <v>-3.400994133333334</v>
+        <v>-3.528301333333334</v>
       </c>
       <c r="O66">
-        <v>-0.7822286506666668</v>
+        <v>-0.8115093066666669</v>
       </c>
       <c r="P66">
-        <v>-2.618765482666667</v>
+        <v>-2.716792026666667</v>
       </c>
       <c r="Q66">
-        <v>0.2012345173333334</v>
+        <v>0.1032079733333329</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.184439617127953</v>
+        <v>0.1884007490458945</v>
       </c>
       <c r="T66">
-        <v>2.144710784287565</v>
+        <v>2.20598823526721</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1339934688166367</v>
+        <v>0.1319320308348423</v>
       </c>
       <c r="W66">
-        <v>0.1738941114616194</v>
+        <v>0.1743080482083637</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5825802992027683</v>
+        <v>0.5736175253688796</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1792404935014995</v>
+        <v>0.1807904935014995</v>
       </c>
       <c r="C67">
-        <v>-13.71331314185863</v>
+        <v>-14.62583545594811</v>
       </c>
       <c r="D67">
-        <v>24.25668685814137</v>
+        <v>23.97816454405189</v>
       </c>
       <c r="E67">
-        <v>11.11</v>
+        <v>11.744</v>
       </c>
       <c r="F67">
-        <v>41.21</v>
+        <v>41.844</v>
       </c>
       <c r="G67">
         <v>3.24</v>
@@ -6769,37 +6769,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M67">
-        <v>8.274968000000001</v>
+        <v>8.4022752</v>
       </c>
       <c r="N67">
-        <v>-3.528301333333334</v>
+        <v>-3.655608533333333</v>
       </c>
       <c r="O67">
-        <v>-0.8115093066666669</v>
+        <v>-0.8407899626666666</v>
       </c>
       <c r="P67">
-        <v>-2.716792026666667</v>
+        <v>-2.814818570666667</v>
       </c>
       <c r="Q67">
-        <v>0.1032079733333329</v>
+        <v>0.005181429333333654</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1884007490458945</v>
+        <v>0.1925948887237149</v>
       </c>
       <c r="T67">
-        <v>2.20598823526721</v>
+        <v>2.270870242186834</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1319320308348423</v>
+        <v>0.129933060670678</v>
       </c>
       <c r="W67">
-        <v>0.1743080482083637</v>
+        <v>0.1747094414173279</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5736175253688796</v>
+        <v>0.5649263507420784</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1807904935014995</v>
+        <v>0.1823404935014995</v>
       </c>
       <c r="C68">
-        <v>-14.62583545594811</v>
+        <v>-15.53203423075973</v>
       </c>
       <c r="D68">
-        <v>23.97816454405189</v>
+        <v>23.70596576924028</v>
       </c>
       <c r="E68">
-        <v>11.744</v>
+        <v>12.378</v>
       </c>
       <c r="F68">
-        <v>41.844</v>
+        <v>42.478</v>
       </c>
       <c r="G68">
         <v>3.24</v>
@@ -6851,37 +6851,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M68">
-        <v>8.4022752</v>
+        <v>8.529582400000001</v>
       </c>
       <c r="N68">
-        <v>-3.655608533333333</v>
+        <v>-3.782915733333334</v>
       </c>
       <c r="O68">
-        <v>-0.8407899626666666</v>
+        <v>-0.8700706186666668</v>
       </c>
       <c r="P68">
-        <v>-2.814818570666667</v>
+        <v>-2.912845114666667</v>
       </c>
       <c r="Q68">
-        <v>0.005181429333333654</v>
+        <v>-0.09284511466666645</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1925948887237149</v>
+        <v>0.1970432186850397</v>
       </c>
       <c r="T68">
-        <v>2.270870242186834</v>
+        <v>2.339684491950072</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.129933060670678</v>
+        <v>0.1279937612576828</v>
       </c>
       <c r="W68">
-        <v>0.1747094414173279</v>
+        <v>0.1750988527394573</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5649263507420784</v>
+        <v>0.5564946141638384</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1823404935014995</v>
+        <v>0.1838904935014995</v>
       </c>
       <c r="C69">
-        <v>-15.53203423075973</v>
+        <v>-16.43212240244059</v>
       </c>
       <c r="D69">
-        <v>23.70596576924028</v>
+        <v>23.43987759755941</v>
       </c>
       <c r="E69">
-        <v>12.378</v>
+        <v>13.012</v>
       </c>
       <c r="F69">
-        <v>42.478</v>
+        <v>43.112</v>
       </c>
       <c r="G69">
         <v>3.24</v>
@@ -6933,37 +6933,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M69">
-        <v>8.529582400000001</v>
+        <v>8.656889600000001</v>
       </c>
       <c r="N69">
-        <v>-3.782915733333334</v>
+        <v>-3.910222933333334</v>
       </c>
       <c r="O69">
-        <v>-0.8700706186666668</v>
+        <v>-0.8993512746666669</v>
       </c>
       <c r="P69">
-        <v>-2.912845114666667</v>
+        <v>-3.010871658666667</v>
       </c>
       <c r="Q69">
-        <v>-0.09284511466666645</v>
+        <v>-0.190871658666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1970432186850397</v>
+        <v>0.2017695692689471</v>
       </c>
       <c r="T69">
-        <v>2.339684491950072</v>
+        <v>2.412799632323511</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1279937612576828</v>
+        <v>0.1261115000627169</v>
       </c>
       <c r="W69">
-        <v>0.1750988527394573</v>
+        <v>0.1754768107874065</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5564946141638384</v>
+        <v>0.5483108698378996</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1838904935014995</v>
+        <v>0.1854404935014995</v>
       </c>
       <c r="C70">
-        <v>-16.43212240244059</v>
+        <v>-17.32630345283073</v>
       </c>
       <c r="D70">
-        <v>23.43987759755941</v>
+        <v>23.17969654716928</v>
       </c>
       <c r="E70">
-        <v>13.012</v>
+        <v>13.646</v>
       </c>
       <c r="F70">
-        <v>43.112</v>
+        <v>43.746</v>
       </c>
       <c r="G70">
         <v>3.24</v>
@@ -7015,37 +7015,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M70">
-        <v>8.656889600000001</v>
+        <v>8.7841968</v>
       </c>
       <c r="N70">
-        <v>-3.910222933333334</v>
+        <v>-4.037530133333333</v>
       </c>
       <c r="O70">
-        <v>-0.8993512746666669</v>
+        <v>-0.9286319306666666</v>
       </c>
       <c r="P70">
-        <v>-3.010871658666667</v>
+        <v>-3.108898202666666</v>
       </c>
       <c r="Q70">
-        <v>-0.190871658666667</v>
+        <v>-0.2888982026666662</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2017695692689471</v>
+        <v>0.2068008456969777</v>
       </c>
       <c r="T70">
-        <v>2.412799632323511</v>
+        <v>2.490631878527496</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1261115000627169</v>
+        <v>0.1242837971632572</v>
       </c>
       <c r="W70">
-        <v>0.1754768107874065</v>
+        <v>0.1758438135296179</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5483108698378996</v>
+        <v>0.5403643354924228</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1854404935014995</v>
+        <v>0.1869904935014995</v>
       </c>
       <c r="C71">
-        <v>-17.32630345283073</v>
+        <v>-18.21477192841355</v>
       </c>
       <c r="D71">
-        <v>23.17969654716928</v>
+        <v>22.92522807158646</v>
       </c>
       <c r="E71">
-        <v>13.646</v>
+        <v>14.28</v>
       </c>
       <c r="F71">
-        <v>43.746</v>
+        <v>44.38</v>
       </c>
       <c r="G71">
         <v>3.24</v>
@@ -7097,37 +7097,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M71">
-        <v>8.7841968</v>
+        <v>8.911504000000001</v>
       </c>
       <c r="N71">
-        <v>-4.037530133333333</v>
+        <v>-4.164837333333334</v>
       </c>
       <c r="O71">
-        <v>-0.9286319306666666</v>
+        <v>-0.9579125866666668</v>
       </c>
       <c r="P71">
-        <v>-3.108898202666666</v>
+        <v>-3.206924746666667</v>
       </c>
       <c r="Q71">
-        <v>-0.2888982026666662</v>
+        <v>-0.3869247466666668</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2068008456969777</v>
+        <v>0.2121675405535436</v>
       </c>
       <c r="T71">
-        <v>2.490631878527496</v>
+        <v>2.573652941145079</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1242837971632572</v>
+        <v>0.1225083143466393</v>
       </c>
       <c r="W71">
-        <v>0.1758438135296179</v>
+        <v>0.1762003304791948</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5403643354924228</v>
+        <v>0.5326448449853882</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1869904935014995</v>
+        <v>0.1885404935014995</v>
       </c>
       <c r="C72">
-        <v>-18.21477192841355</v>
+        <v>-19.0977139254551</v>
       </c>
       <c r="D72">
-        <v>22.92522807158646</v>
+        <v>22.67628607454491</v>
       </c>
       <c r="E72">
-        <v>14.28</v>
+        <v>14.914</v>
       </c>
       <c r="F72">
-        <v>44.38</v>
+        <v>45.014</v>
       </c>
       <c r="G72">
         <v>3.24</v>
@@ -7179,37 +7179,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M72">
-        <v>8.911504000000001</v>
+        <v>9.038811200000001</v>
       </c>
       <c r="N72">
-        <v>-4.164837333333334</v>
+        <v>-4.292144533333334</v>
       </c>
       <c r="O72">
-        <v>-0.9579125866666668</v>
+        <v>-0.987193242666667</v>
       </c>
       <c r="P72">
-        <v>-3.206924746666667</v>
+        <v>-3.304951290666668</v>
       </c>
       <c r="Q72">
-        <v>-0.3869247466666668</v>
+        <v>-0.4849512906666673</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2121675405535436</v>
+        <v>0.2179043522967692</v>
       </c>
       <c r="T72">
-        <v>2.573652941145079</v>
+        <v>2.662399594288013</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1225083143466393</v>
+        <v>0.1207828451304894</v>
       </c>
       <c r="W72">
-        <v>0.1762003304791948</v>
+        <v>0.1765468046977977</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5326448449853882</v>
+        <v>0.5251428049151714</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1885404935014995</v>
+        <v>0.1900904935014995</v>
       </c>
       <c r="C73">
-        <v>-19.09771392545508</v>
+        <v>-19.97530754387444</v>
       </c>
       <c r="D73">
-        <v>22.67628607454492</v>
+        <v>22.43269245612556</v>
       </c>
       <c r="E73">
-        <v>14.91399999999999</v>
+        <v>15.54799999999999</v>
       </c>
       <c r="F73">
-        <v>45.014</v>
+        <v>45.648</v>
       </c>
       <c r="G73">
         <v>3.24</v>
@@ -7261,37 +7261,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M73">
-        <v>9.0388112</v>
+        <v>9.1661184</v>
       </c>
       <c r="N73">
-        <v>-4.292144533333333</v>
+        <v>-4.419451733333333</v>
       </c>
       <c r="O73">
-        <v>-0.9871932426666665</v>
+        <v>-1.016473898666667</v>
       </c>
       <c r="P73">
-        <v>-3.304951290666666</v>
+        <v>-3.402977834666666</v>
       </c>
       <c r="Q73">
-        <v>-0.4849512906666655</v>
+        <v>-0.5829778346666661</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2179043522967692</v>
+        <v>0.2240509363073681</v>
       </c>
       <c r="T73">
-        <v>2.662399594288012</v>
+        <v>2.757485294084013</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1207828451304895</v>
+        <v>0.1191053056147882</v>
       </c>
       <c r="W73">
-        <v>0.1765468046977977</v>
+        <v>0.1768836546325505</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5251428049151715</v>
+        <v>0.5178491548469052</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1900904935014995</v>
+        <v>0.1916404935014995</v>
       </c>
       <c r="C74">
-        <v>-19.97530754387444</v>
+        <v>-20.84772331217158</v>
       </c>
       <c r="D74">
-        <v>22.43269245612556</v>
+        <v>22.19427668782842</v>
       </c>
       <c r="E74">
-        <v>15.54799999999999</v>
+        <v>16.182</v>
       </c>
       <c r="F74">
-        <v>45.648</v>
+        <v>46.282</v>
       </c>
       <c r="G74">
         <v>3.24</v>
@@ -7343,37 +7343,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M74">
-        <v>9.1661184</v>
+        <v>9.293425599999999</v>
       </c>
       <c r="N74">
-        <v>-4.419451733333333</v>
+        <v>-4.546758933333332</v>
       </c>
       <c r="O74">
-        <v>-1.016473898666667</v>
+        <v>-1.045754554666666</v>
       </c>
       <c r="P74">
-        <v>-3.402977834666666</v>
+        <v>-3.501004378666666</v>
       </c>
       <c r="Q74">
-        <v>-0.5829778346666661</v>
+        <v>-0.6810043786666653</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2240509363073681</v>
+        <v>0.2306528228372706</v>
       </c>
       <c r="T74">
-        <v>2.757485294084013</v>
+        <v>2.859614379050087</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1191053056147882</v>
+        <v>0.1174737260858185</v>
       </c>
       <c r="W74">
-        <v>0.1768836546325505</v>
+        <v>0.1772112758019677</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5178491548469052</v>
+        <v>0.5107553308079066</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1916404935014995</v>
+        <v>0.1931904935014994</v>
       </c>
       <c r="C75">
-        <v>-20.84772331217158</v>
+        <v>-21.71512458554328</v>
       </c>
       <c r="D75">
-        <v>22.19427668782842</v>
+        <v>21.96087541445672</v>
       </c>
       <c r="E75">
-        <v>16.182</v>
+        <v>16.816</v>
       </c>
       <c r="F75">
-        <v>46.282</v>
+        <v>46.916</v>
       </c>
       <c r="G75">
         <v>3.24</v>
@@ -7425,37 +7425,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M75">
-        <v>9.293425599999999</v>
+        <v>9.4207328</v>
       </c>
       <c r="N75">
-        <v>-4.546758933333332</v>
+        <v>-4.674066133333333</v>
       </c>
       <c r="O75">
-        <v>-1.045754554666666</v>
+        <v>-1.075035210666667</v>
       </c>
       <c r="P75">
-        <v>-3.501004378666666</v>
+        <v>-3.599030922666666</v>
       </c>
       <c r="Q75">
-        <v>-0.6810043786666653</v>
+        <v>-0.7790309226666658</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2306528228372706</v>
+        <v>0.2377625467925503</v>
       </c>
       <c r="T75">
-        <v>2.859614379050087</v>
+        <v>2.96959954747509</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1174737260858185</v>
+        <v>0.115886243300875</v>
       </c>
       <c r="W75">
-        <v>0.1772112758019677</v>
+        <v>0.1775300423451843</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5107553308079066</v>
+        <v>0.5038532317429348</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1931904935014994</v>
+        <v>0.2216853825938533</v>
       </c>
       <c r="C76">
-        <v>-21.71512458554328</v>
+        <v>-25.90696833627128</v>
       </c>
       <c r="D76">
-        <v>21.96087541445672</v>
+        <v>18.40303166372871</v>
       </c>
       <c r="E76">
-        <v>16.816</v>
+        <v>17.45</v>
       </c>
       <c r="F76">
-        <v>46.916</v>
+        <v>47.55</v>
       </c>
       <c r="G76">
         <v>3.24</v>
@@ -7507,45 +7507,45 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M76">
-        <v>9.4207328</v>
+        <v>11.21229</v>
       </c>
       <c r="N76">
-        <v>-4.674066133333333</v>
+        <v>-6.465623333333332</v>
       </c>
       <c r="O76">
-        <v>-1.075035210666667</v>
+        <v>-1.487093366666667</v>
       </c>
       <c r="P76">
-        <v>-3.599030922666666</v>
+        <v>-4.978529966666666</v>
       </c>
       <c r="Q76">
-        <v>-0.7790309226666658</v>
+        <v>-2.158529966666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2377625467925503</v>
+        <v>0.2482206050336676</v>
       </c>
       <c r="T76">
-        <v>2.96959954747509</v>
+        <v>3.131382382404094</v>
       </c>
       <c r="U76">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.115886243300875</v>
+        <v>0.09736934500742787</v>
       </c>
       <c r="W76">
-        <v>0.1775300423451843</v>
+        <v>0.2128403084472485</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.5038532317429348</v>
+        <v>0.4233449782931646</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2216853825938533</v>
+        <v>0.2235853825938533</v>
       </c>
       <c r="C77">
-        <v>-25.90696833627128</v>
+        <v>-26.73764232403642</v>
       </c>
       <c r="D77">
-        <v>18.40303166372871</v>
+        <v>18.20635767596357</v>
       </c>
       <c r="E77">
-        <v>17.45</v>
+        <v>18.084</v>
       </c>
       <c r="F77">
-        <v>47.55</v>
+        <v>48.184</v>
       </c>
       <c r="G77">
         <v>3.24</v>
@@ -7589,37 +7589,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M77">
-        <v>11.21229</v>
+        <v>11.3617872</v>
       </c>
       <c r="N77">
-        <v>-6.465623333333332</v>
+        <v>-6.615120533333333</v>
       </c>
       <c r="O77">
-        <v>-1.487093366666667</v>
+        <v>-1.521477722666667</v>
       </c>
       <c r="P77">
-        <v>-4.978529966666666</v>
+        <v>-5.093642810666666</v>
       </c>
       <c r="Q77">
-        <v>-2.158529966666666</v>
+        <v>-2.273642810666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2482206050336676</v>
+        <v>0.2566547969100704</v>
       </c>
       <c r="T77">
-        <v>3.131382382404094</v>
+        <v>3.261856648337597</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09736934500742787</v>
+        <v>0.09608816941522487</v>
       </c>
       <c r="W77">
-        <v>0.2128403084472485</v>
+        <v>0.21314240965189</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4233449782931646</v>
+        <v>0.4177746496314124</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2235853825938533</v>
+        <v>0.2254853825938533</v>
       </c>
       <c r="C78">
-        <v>-26.73764232403642</v>
+        <v>-27.56415703550031</v>
       </c>
       <c r="D78">
-        <v>18.20635767596357</v>
+        <v>18.01384296449969</v>
       </c>
       <c r="E78">
-        <v>18.084</v>
+        <v>18.718</v>
       </c>
       <c r="F78">
-        <v>48.184</v>
+        <v>48.818</v>
       </c>
       <c r="G78">
         <v>3.24</v>
@@ -7671,37 +7671,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M78">
-        <v>11.3617872</v>
+        <v>11.5112844</v>
       </c>
       <c r="N78">
-        <v>-6.615120533333333</v>
+        <v>-6.764617733333332</v>
       </c>
       <c r="O78">
-        <v>-1.521477722666667</v>
+        <v>-1.555862078666666</v>
       </c>
       <c r="P78">
-        <v>-5.093642810666666</v>
+        <v>-5.208755654666666</v>
       </c>
       <c r="Q78">
-        <v>-2.273642810666666</v>
+        <v>-2.388755654666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2566547969100704</v>
+        <v>0.2658223967757257</v>
       </c>
       <c r="T78">
-        <v>3.261856648337597</v>
+        <v>3.403676502613146</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09608816941522487</v>
+        <v>0.09484027111113105</v>
       </c>
       <c r="W78">
-        <v>0.21314240965189</v>
+        <v>0.2134366640719953</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4177746496314124</v>
+        <v>0.4123490048310046</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2254853825938533</v>
+        <v>0.2273853825938533</v>
       </c>
       <c r="C79">
-        <v>-27.56415703550031</v>
+        <v>-28.38664303114403</v>
       </c>
       <c r="D79">
-        <v>18.01384296449969</v>
+        <v>17.82535696885597</v>
       </c>
       <c r="E79">
-        <v>18.718</v>
+        <v>19.352</v>
       </c>
       <c r="F79">
-        <v>48.818</v>
+        <v>49.452</v>
       </c>
       <c r="G79">
         <v>3.24</v>
@@ -7753,37 +7753,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M79">
-        <v>11.5112844</v>
+        <v>11.6607816</v>
       </c>
       <c r="N79">
-        <v>-6.764617733333332</v>
+        <v>-6.914114933333333</v>
       </c>
       <c r="O79">
-        <v>-1.555862078666666</v>
+        <v>-1.590246434666667</v>
       </c>
       <c r="P79">
-        <v>-5.208755654666666</v>
+        <v>-5.323868498666666</v>
       </c>
       <c r="Q79">
-        <v>-2.388755654666666</v>
+        <v>-2.503868498666666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2658223967757257</v>
+        <v>0.2758234148109859</v>
       </c>
       <c r="T79">
-        <v>3.403676502613146</v>
+        <v>3.558389070913742</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09484027111113105</v>
+        <v>0.09362437019944989</v>
       </c>
       <c r="W79">
-        <v>0.2134366640719953</v>
+        <v>0.2137233735069697</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4123490048310046</v>
+        <v>0.4070624791280429</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2273853825938533</v>
+        <v>0.2292853825938533</v>
       </c>
       <c r="C80">
-        <v>-28.38664303114403</v>
+        <v>-29.20522546360837</v>
       </c>
       <c r="D80">
-        <v>17.82535696885597</v>
+        <v>17.64077453639162</v>
       </c>
       <c r="E80">
-        <v>19.352</v>
+        <v>19.986</v>
       </c>
       <c r="F80">
-        <v>49.452</v>
+        <v>50.086</v>
       </c>
       <c r="G80">
         <v>3.24</v>
@@ -7835,37 +7835,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M80">
-        <v>11.6607816</v>
+        <v>11.8102788</v>
       </c>
       <c r="N80">
-        <v>-6.914114933333333</v>
+        <v>-7.063612133333334</v>
       </c>
       <c r="O80">
-        <v>-1.590246434666667</v>
+        <v>-1.624630790666667</v>
       </c>
       <c r="P80">
-        <v>-5.323868498666666</v>
+        <v>-5.438981342666667</v>
       </c>
       <c r="Q80">
-        <v>-2.503868498666666</v>
+        <v>-2.618981342666666</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2758234148109859</v>
+        <v>0.2867769107543663</v>
       </c>
       <c r="T80">
-        <v>3.558389070913742</v>
+        <v>3.727836169528684</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09362437019944989</v>
+        <v>0.09243925158933025</v>
       </c>
       <c r="W80">
-        <v>0.2137233735069697</v>
+        <v>0.2140028244752359</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4070624791280429</v>
+        <v>0.4019097895188272</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2292853825938533</v>
+        <v>0.2311853825938533</v>
       </c>
       <c r="C81">
-        <v>-29.20522546360837</v>
+        <v>-30.0200243548164</v>
       </c>
       <c r="D81">
-        <v>17.64077453639162</v>
+        <v>17.4599756451836</v>
       </c>
       <c r="E81">
-        <v>19.986</v>
+        <v>20.62</v>
       </c>
       <c r="F81">
-        <v>50.086</v>
+        <v>50.72</v>
       </c>
       <c r="G81">
         <v>3.24</v>
@@ -7917,37 +7917,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M81">
-        <v>11.8102788</v>
+        <v>11.959776</v>
       </c>
       <c r="N81">
-        <v>-7.063612133333334</v>
+        <v>-7.213109333333333</v>
       </c>
       <c r="O81">
-        <v>-1.624630790666667</v>
+        <v>-1.659015146666666</v>
       </c>
       <c r="P81">
-        <v>-5.438981342666667</v>
+        <v>-5.554094186666666</v>
       </c>
       <c r="Q81">
-        <v>-2.618981342666666</v>
+        <v>-2.734094186666666</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2867769107543663</v>
+        <v>0.2988257562920845</v>
       </c>
       <c r="T81">
-        <v>3.727836169528684</v>
+        <v>3.914227978005117</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09243925158933025</v>
+        <v>0.09128376094446362</v>
       </c>
       <c r="W81">
-        <v>0.2140028244752359</v>
+        <v>0.2142752891692955</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4019097895188272</v>
+        <v>0.3968859171498419</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2311853825938533</v>
+        <v>0.2330853825938533</v>
       </c>
       <c r="C82">
-        <v>-30.0200243548164</v>
+        <v>-30.83115485622767</v>
       </c>
       <c r="D82">
-        <v>17.4599756451836</v>
+        <v>17.28284514377233</v>
       </c>
       <c r="E82">
-        <v>20.62</v>
+        <v>21.254</v>
       </c>
       <c r="F82">
-        <v>50.72</v>
+        <v>51.354</v>
       </c>
       <c r="G82">
         <v>3.24</v>
@@ -7999,37 +7999,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M82">
-        <v>11.959776</v>
+        <v>12.1092732</v>
       </c>
       <c r="N82">
-        <v>-7.213109333333333</v>
+        <v>-7.362606533333333</v>
       </c>
       <c r="O82">
-        <v>-1.659015146666666</v>
+        <v>-1.693399502666667</v>
       </c>
       <c r="P82">
-        <v>-5.554094186666666</v>
+        <v>-5.669207030666667</v>
       </c>
       <c r="Q82">
-        <v>-2.734094186666666</v>
+        <v>-2.849207030666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2988257562920845</v>
+        <v>0.3121429013600891</v>
       </c>
       <c r="T82">
-        <v>3.914227978005117</v>
+        <v>4.120239976847493</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09128376094446362</v>
+        <v>0.09015680093280358</v>
       </c>
       <c r="W82">
-        <v>0.2142752891692955</v>
+        <v>0.2145410263400449</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3968859171498419</v>
+        <v>0.3919860910121895</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2330853825938533</v>
+        <v>0.2349853825938533</v>
       </c>
       <c r="C83">
-        <v>-30.83115485622767</v>
+        <v>-31.63872749341002</v>
       </c>
       <c r="D83">
-        <v>17.28284514377233</v>
+        <v>17.10927250658997</v>
       </c>
       <c r="E83">
-        <v>21.254</v>
+        <v>21.888</v>
       </c>
       <c r="F83">
-        <v>51.354</v>
+        <v>51.988</v>
       </c>
       <c r="G83">
         <v>3.24</v>
@@ -8081,37 +8081,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M83">
-        <v>12.1092732</v>
+        <v>12.2587704</v>
       </c>
       <c r="N83">
-        <v>-7.362606533333333</v>
+        <v>-7.512103733333332</v>
       </c>
       <c r="O83">
-        <v>-1.693399502666667</v>
+        <v>-1.727783858666667</v>
       </c>
       <c r="P83">
-        <v>-5.669207030666667</v>
+        <v>-5.784319874666666</v>
       </c>
       <c r="Q83">
-        <v>-2.849207030666666</v>
+        <v>-2.964319874666666</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3121429013600891</v>
+        <v>0.3269397292134273</v>
       </c>
       <c r="T83">
-        <v>4.120239976847493</v>
+        <v>4.349142197783465</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09015680093280358</v>
+        <v>0.08905732775069622</v>
       </c>
       <c r="W83">
-        <v>0.2145410263400449</v>
+        <v>0.2148002821163859</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3919860910121895</v>
+        <v>0.3872057728291141</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2349853825938533</v>
+        <v>0.2368853825938533</v>
       </c>
       <c r="C84">
-        <v>-31.63872749341002</v>
+        <v>-32.44284839602042</v>
       </c>
       <c r="D84">
-        <v>17.10927250658997</v>
+        <v>16.93915160397958</v>
       </c>
       <c r="E84">
-        <v>21.888</v>
+        <v>22.522</v>
       </c>
       <c r="F84">
-        <v>51.988</v>
+        <v>52.622</v>
       </c>
       <c r="G84">
         <v>3.24</v>
@@ -8163,37 +8163,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M84">
-        <v>12.2587704</v>
+        <v>12.4082676</v>
       </c>
       <c r="N84">
-        <v>-7.512103733333332</v>
+        <v>-7.661600933333333</v>
       </c>
       <c r="O84">
-        <v>-1.727783858666667</v>
+        <v>-1.762168214666667</v>
       </c>
       <c r="P84">
-        <v>-5.784319874666666</v>
+        <v>-5.899432718666667</v>
       </c>
       <c r="Q84">
-        <v>-2.964319874666666</v>
+        <v>-3.079432718666666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3269397292134273</v>
+        <v>0.3434773603436289</v>
       </c>
       <c r="T84">
-        <v>4.349142197783465</v>
+        <v>4.604974091770726</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08905732775069622</v>
+        <v>0.08798434789827821</v>
       </c>
       <c r="W84">
-        <v>0.2148002821163859</v>
+        <v>0.215053290765586</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3872057728291141</v>
+        <v>0.3825406430359921</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2368853825938533</v>
+        <v>0.2387853825938533</v>
       </c>
       <c r="C85">
-        <v>-32.44284839602042</v>
+        <v>-33.24361951420038</v>
       </c>
       <c r="D85">
-        <v>16.93915160397958</v>
+        <v>16.77238048579962</v>
       </c>
       <c r="E85">
-        <v>22.522</v>
+        <v>23.15600000000001</v>
       </c>
       <c r="F85">
-        <v>52.622</v>
+        <v>53.25600000000001</v>
       </c>
       <c r="G85">
         <v>3.24</v>
@@ -8245,37 +8245,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M85">
-        <v>12.4082676</v>
+        <v>12.5577648</v>
       </c>
       <c r="N85">
-        <v>-7.661600933333333</v>
+        <v>-7.811098133333336</v>
       </c>
       <c r="O85">
-        <v>-1.762168214666667</v>
+        <v>-1.796552570666667</v>
       </c>
       <c r="P85">
-        <v>-5.899432718666667</v>
+        <v>-6.014545562666669</v>
       </c>
       <c r="Q85">
-        <v>-3.079432718666666</v>
+        <v>-3.194545562666669</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3434773603436289</v>
+        <v>0.3620821953651058</v>
       </c>
       <c r="T85">
-        <v>4.604974091770726</v>
+        <v>4.892784972506399</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08798434789827821</v>
+        <v>0.08693691518520344</v>
       </c>
       <c r="W85">
-        <v>0.215053290765586</v>
+        <v>0.2153002753993291</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3825406430359921</v>
+        <v>0.3779865877617541</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2387853825938533</v>
+        <v>0.2406853825938533</v>
       </c>
       <c r="C86">
-        <v>-33.24361951420037</v>
+        <v>-34.04113882231303</v>
       </c>
       <c r="D86">
-        <v>16.77238048579963</v>
+        <v>16.60886117768697</v>
       </c>
       <c r="E86">
-        <v>23.156</v>
+        <v>23.79</v>
       </c>
       <c r="F86">
-        <v>53.256</v>
+        <v>53.89</v>
       </c>
       <c r="G86">
         <v>3.24</v>
@@ -8327,37 +8327,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M86">
-        <v>12.5577648</v>
+        <v>12.707262</v>
       </c>
       <c r="N86">
-        <v>-7.811098133333334</v>
+        <v>-7.960595333333333</v>
       </c>
       <c r="O86">
-        <v>-1.796552570666667</v>
+        <v>-1.830936926666667</v>
       </c>
       <c r="P86">
-        <v>-6.014545562666667</v>
+        <v>-6.129658406666667</v>
       </c>
       <c r="Q86">
-        <v>-3.194545562666667</v>
+        <v>-3.309658406666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3620821953651057</v>
+        <v>0.3831676750561126</v>
       </c>
       <c r="T86">
-        <v>4.892784972506396</v>
+        <v>5.218970637340155</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08693691518520344</v>
+        <v>0.08591412794773047</v>
       </c>
       <c r="W86">
-        <v>0.2153002753993291</v>
+        <v>0.2155414486299252</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3779865877617541</v>
+        <v>0.373539686729263</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2406853825938533</v>
+        <v>0.2425853825938533</v>
       </c>
       <c r="C87">
-        <v>-34.04113882231303</v>
+        <v>-34.83550051087776</v>
       </c>
       <c r="D87">
-        <v>16.60886117768697</v>
+        <v>16.44849948912224</v>
       </c>
       <c r="E87">
-        <v>23.79</v>
+        <v>24.424</v>
       </c>
       <c r="F87">
-        <v>53.89</v>
+        <v>54.524</v>
       </c>
       <c r="G87">
         <v>3.24</v>
@@ -8409,37 +8409,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M87">
-        <v>12.707262</v>
+        <v>12.8567592</v>
       </c>
       <c r="N87">
-        <v>-7.960595333333333</v>
+        <v>-8.110092533333333</v>
       </c>
       <c r="O87">
-        <v>-1.830936926666667</v>
+        <v>-1.865321282666667</v>
       </c>
       <c r="P87">
-        <v>-6.129658406666667</v>
+        <v>-6.244771250666666</v>
       </c>
       <c r="Q87">
-        <v>-3.309658406666666</v>
+        <v>-3.424771250666666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3831676750561126</v>
+        <v>0.4072653661315493</v>
       </c>
       <c r="T87">
-        <v>5.218970637340155</v>
+        <v>5.591754254293024</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08591412794773047</v>
+        <v>0.08491512645996617</v>
       </c>
       <c r="W87">
-        <v>0.2155414486299252</v>
+        <v>0.21577701318074</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.373539686729263</v>
+        <v>0.3691962019998529</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2425853825938533</v>
+        <v>0.2444853825938533</v>
       </c>
       <c r="C88">
-        <v>-34.83550051087776</v>
+        <v>-35.62679516749181</v>
       </c>
       <c r="D88">
-        <v>16.44849948912224</v>
+        <v>16.2912048325082</v>
       </c>
       <c r="E88">
-        <v>24.424</v>
+        <v>25.058</v>
       </c>
       <c r="F88">
-        <v>54.524</v>
+        <v>55.158</v>
       </c>
       <c r="G88">
         <v>3.24</v>
@@ -8491,37 +8491,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M88">
-        <v>12.8567592</v>
+        <v>13.0062564</v>
       </c>
       <c r="N88">
-        <v>-8.110092533333333</v>
+        <v>-8.259589733333335</v>
       </c>
       <c r="O88">
-        <v>-1.865321282666667</v>
+        <v>-1.899705638666667</v>
       </c>
       <c r="P88">
-        <v>-6.244771250666666</v>
+        <v>-6.359884094666668</v>
       </c>
       <c r="Q88">
-        <v>-3.424771250666666</v>
+        <v>-3.539884094666668</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4072653661315493</v>
+        <v>0.4350703942955146</v>
       </c>
       <c r="T88">
-        <v>5.591754254293024</v>
+        <v>6.021889196930949</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08491512645996617</v>
+        <v>0.08393909052364472</v>
       </c>
       <c r="W88">
-        <v>0.21577701318074</v>
+        <v>0.2160071624545246</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3691962019998529</v>
+        <v>0.3649525674941073</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2444853825938533</v>
+        <v>0.2463853825938533</v>
       </c>
       <c r="C89">
-        <v>-35.62679516749181</v>
+        <v>-36.41510994746978</v>
       </c>
       <c r="D89">
-        <v>16.2912048325082</v>
+        <v>16.13689005253022</v>
       </c>
       <c r="E89">
-        <v>25.058</v>
+        <v>25.692</v>
       </c>
       <c r="F89">
-        <v>55.158</v>
+        <v>55.792</v>
       </c>
       <c r="G89">
         <v>3.24</v>
@@ -8573,37 +8573,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M89">
-        <v>13.0062564</v>
+        <v>13.1557536</v>
       </c>
       <c r="N89">
-        <v>-8.259589733333335</v>
+        <v>-8.409086933333334</v>
       </c>
       <c r="O89">
-        <v>-1.899705638666667</v>
+        <v>-1.934089994666667</v>
       </c>
       <c r="P89">
-        <v>-6.359884094666668</v>
+        <v>-6.474996938666667</v>
       </c>
       <c r="Q89">
-        <v>-3.539884094666668</v>
+        <v>-3.654996938666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4350703942955146</v>
+        <v>0.4675095938201408</v>
       </c>
       <c r="T89">
-        <v>6.021889196930949</v>
+        <v>6.523713296675195</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08393909052364472</v>
+        <v>0.08298523722223966</v>
       </c>
       <c r="W89">
-        <v>0.2160071624545246</v>
+        <v>0.2162320810629959</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3649525674941073</v>
+        <v>0.3608053792271289</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2463853825938533</v>
+        <v>0.2482853825938533</v>
       </c>
       <c r="C90">
-        <v>-36.41510994746978</v>
+        <v>-37.20052873487581</v>
       </c>
       <c r="D90">
-        <v>16.13689005253022</v>
+        <v>15.98547126512419</v>
       </c>
       <c r="E90">
-        <v>25.692</v>
+        <v>26.326</v>
       </c>
       <c r="F90">
-        <v>55.792</v>
+        <v>56.426</v>
       </c>
       <c r="G90">
         <v>3.24</v>
@@ -8655,37 +8655,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M90">
-        <v>13.1557536</v>
+        <v>13.3052508</v>
       </c>
       <c r="N90">
-        <v>-8.409086933333334</v>
+        <v>-8.558584133333333</v>
       </c>
       <c r="O90">
-        <v>-1.934089994666667</v>
+        <v>-1.968474350666667</v>
       </c>
       <c r="P90">
-        <v>-6.474996938666667</v>
+        <v>-6.590109782666667</v>
       </c>
       <c r="Q90">
-        <v>-3.654996938666667</v>
+        <v>-3.770109782666666</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4675095938201408</v>
+        <v>0.5058468296219718</v>
       </c>
       <c r="T90">
-        <v>6.523713296675195</v>
+        <v>7.116778141827485</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08298523722223966</v>
+        <v>0.08205281882648416</v>
       </c>
       <c r="W90">
-        <v>0.2162320810629959</v>
+        <v>0.216451945320715</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3608053792271289</v>
+        <v>0.3567513862021051</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2482853825938533</v>
+        <v>0.2501853825938533</v>
       </c>
       <c r="C91">
-        <v>-37.20052873487581</v>
+        <v>-37.98313229457406</v>
       </c>
       <c r="D91">
-        <v>15.98547126512419</v>
+        <v>15.83686770542594</v>
       </c>
       <c r="E91">
-        <v>26.326</v>
+        <v>26.96</v>
       </c>
       <c r="F91">
-        <v>56.426</v>
+        <v>57.06</v>
       </c>
       <c r="G91">
         <v>3.24</v>
@@ -8737,37 +8737,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M91">
-        <v>13.3052508</v>
+        <v>13.454748</v>
       </c>
       <c r="N91">
-        <v>-8.558584133333333</v>
+        <v>-8.708081333333332</v>
       </c>
       <c r="O91">
-        <v>-1.968474350666667</v>
+        <v>-2.002858706666667</v>
       </c>
       <c r="P91">
-        <v>-6.590109782666667</v>
+        <v>-6.705222626666666</v>
       </c>
       <c r="Q91">
-        <v>-3.770109782666666</v>
+        <v>-3.885222626666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5058468296219718</v>
+        <v>0.551851512584169</v>
       </c>
       <c r="T91">
-        <v>7.116778141827485</v>
+        <v>7.828455956010234</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08205281882648416</v>
+        <v>0.08114112083952323</v>
       </c>
       <c r="W91">
-        <v>0.216451945320715</v>
+        <v>0.2166669237060404</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3567513862021051</v>
+        <v>0.3527874819109706</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2501853825938533</v>
+        <v>0.2520853825938533</v>
       </c>
       <c r="C92">
-        <v>-37.98313229457406</v>
+        <v>-38.76299841587628</v>
       </c>
       <c r="D92">
-        <v>15.83686770542594</v>
+        <v>15.69100158412372</v>
       </c>
       <c r="E92">
-        <v>26.96</v>
+        <v>27.594</v>
       </c>
       <c r="F92">
-        <v>57.06</v>
+        <v>57.694</v>
       </c>
       <c r="G92">
         <v>3.24</v>
@@ -8819,37 +8819,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M92">
-        <v>13.454748</v>
+        <v>13.6042452</v>
       </c>
       <c r="N92">
-        <v>-8.708081333333332</v>
+        <v>-8.857578533333335</v>
       </c>
       <c r="O92">
-        <v>-2.002858706666667</v>
+        <v>-2.037243062666667</v>
       </c>
       <c r="P92">
-        <v>-6.705222626666666</v>
+        <v>-6.820335470666668</v>
       </c>
       <c r="Q92">
-        <v>-3.885222626666666</v>
+        <v>-4.000335470666668</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.551851512584169</v>
+        <v>0.6080794584268545</v>
       </c>
       <c r="T92">
-        <v>7.828455956010234</v>
+        <v>8.698284395566928</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08114112083952323</v>
+        <v>0.08024946017095703</v>
       </c>
       <c r="W92">
-        <v>0.2166669237060404</v>
+        <v>0.2168771772916883</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3527874819109706</v>
+        <v>0.3489106963954652</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2520853825938533</v>
+        <v>0.2539853825938533</v>
       </c>
       <c r="C93">
-        <v>-38.76299841587628</v>
+        <v>-39.54020204832341</v>
       </c>
       <c r="D93">
-        <v>15.69100158412372</v>
+        <v>15.54779795167659</v>
       </c>
       <c r="E93">
-        <v>27.594</v>
+        <v>28.228</v>
       </c>
       <c r="F93">
-        <v>57.694</v>
+        <v>58.328</v>
       </c>
       <c r="G93">
         <v>3.24</v>
@@ -8901,37 +8901,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M93">
-        <v>13.6042452</v>
+        <v>13.7537424</v>
       </c>
       <c r="N93">
-        <v>-8.857578533333335</v>
+        <v>-9.007075733333334</v>
       </c>
       <c r="O93">
-        <v>-2.037243062666667</v>
+        <v>-2.071627418666667</v>
       </c>
       <c r="P93">
-        <v>-6.820335470666668</v>
+        <v>-6.935448314666667</v>
       </c>
       <c r="Q93">
-        <v>-4.000335470666668</v>
+        <v>-4.115448314666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6080794584268545</v>
+        <v>0.6783643907302116</v>
       </c>
       <c r="T93">
-        <v>8.698284395566928</v>
+        <v>9.785569945012798</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08024946017095703</v>
+        <v>0.07937718342996837</v>
       </c>
       <c r="W93">
-        <v>0.2168771772916883</v>
+        <v>0.2170828601472135</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3489106963954652</v>
+        <v>0.3451181888259495</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2539853825938533</v>
+        <v>0.2558853825938533</v>
       </c>
       <c r="C94">
-        <v>-39.54020204832341</v>
+        <v>-40.31481543009921</v>
       </c>
       <c r="D94">
-        <v>15.54779795167659</v>
+        <v>15.40718456990079</v>
       </c>
       <c r="E94">
-        <v>28.228</v>
+        <v>28.862</v>
       </c>
       <c r="F94">
-        <v>58.328</v>
+        <v>58.962</v>
       </c>
       <c r="G94">
         <v>3.24</v>
@@ -8983,37 +8983,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M94">
-        <v>13.7537424</v>
+        <v>13.9032396</v>
       </c>
       <c r="N94">
-        <v>-9.007075733333334</v>
+        <v>-9.156572933333333</v>
       </c>
       <c r="O94">
-        <v>-2.071627418666667</v>
+        <v>-2.106011774666667</v>
       </c>
       <c r="P94">
-        <v>-6.935448314666667</v>
+        <v>-7.050561158666666</v>
       </c>
       <c r="Q94">
-        <v>-4.115448314666667</v>
+        <v>-4.230561158666665</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6783643907302116</v>
+        <v>0.7687307322630991</v>
       </c>
       <c r="T94">
-        <v>9.785569945012798</v>
+        <v>11.18350850858606</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07937718342996837</v>
+        <v>0.07852366532857086</v>
       </c>
       <c r="W94">
-        <v>0.2170828601472135</v>
+        <v>0.217284119715523</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3451181888259495</v>
+        <v>0.3414072405590038</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2558853825938533</v>
+        <v>0.2577853825938533</v>
       </c>
       <c r="C95">
-        <v>-40.31481543009921</v>
+        <v>-41.08690820953815</v>
       </c>
       <c r="D95">
-        <v>15.40718456990079</v>
+        <v>15.26909179046185</v>
       </c>
       <c r="E95">
-        <v>28.862</v>
+        <v>29.496</v>
       </c>
       <c r="F95">
-        <v>58.962</v>
+        <v>59.596</v>
       </c>
       <c r="G95">
         <v>3.24</v>
@@ -9065,37 +9065,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M95">
-        <v>13.9032396</v>
+        <v>14.0527368</v>
       </c>
       <c r="N95">
-        <v>-9.156572933333333</v>
+        <v>-9.306070133333336</v>
       </c>
       <c r="O95">
-        <v>-2.106011774666667</v>
+        <v>-2.140396130666667</v>
       </c>
       <c r="P95">
-        <v>-7.050561158666666</v>
+        <v>-7.165674002666668</v>
       </c>
       <c r="Q95">
-        <v>-4.230561158666665</v>
+        <v>-4.345674002666668</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7687307322630991</v>
+        <v>0.8892191876402824</v>
       </c>
       <c r="T95">
-        <v>11.18350850858606</v>
+        <v>13.0474265933504</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07852366532857086</v>
+        <v>0.07768830718677755</v>
       </c>
       <c r="W95">
-        <v>0.217284119715523</v>
+        <v>0.2174810971653579</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3414072405590038</v>
+        <v>0.3377752486381632</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2577853825938533</v>
+        <v>0.2596853825938533</v>
       </c>
       <c r="C96">
-        <v>-41.08690820953815</v>
+        <v>-41.85654756015692</v>
       </c>
       <c r="D96">
-        <v>15.26909179046185</v>
+        <v>15.13345243984308</v>
       </c>
       <c r="E96">
-        <v>29.496</v>
+        <v>30.13</v>
       </c>
       <c r="F96">
-        <v>59.596</v>
+        <v>60.23</v>
       </c>
       <c r="G96">
         <v>3.24</v>
@@ -9147,37 +9147,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M96">
-        <v>14.0527368</v>
+        <v>14.202234</v>
       </c>
       <c r="N96">
-        <v>-9.306070133333336</v>
+        <v>-9.455567333333335</v>
       </c>
       <c r="O96">
-        <v>-2.140396130666667</v>
+        <v>-2.174780486666667</v>
       </c>
       <c r="P96">
-        <v>-7.165674002666668</v>
+        <v>-7.280786846666667</v>
       </c>
       <c r="Q96">
-        <v>-4.345674002666668</v>
+        <v>-4.460786846666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8892191876402824</v>
+        <v>1.057903025168339</v>
       </c>
       <c r="T96">
-        <v>13.0474265933504</v>
+        <v>15.65691191202049</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07768830718677755</v>
+        <v>0.0768705355321799</v>
       </c>
       <c r="W96">
-        <v>0.2174810971653579</v>
+        <v>0.217673927721512</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3377752486381632</v>
+        <v>0.3342197197051299</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2596853825938533</v>
+        <v>0.2615853825938533</v>
       </c>
       <c r="C97">
-        <v>-41.85654756015692</v>
+        <v>-42.62379828960889</v>
       </c>
       <c r="D97">
-        <v>15.13345243984308</v>
+        <v>15.00020171039112</v>
       </c>
       <c r="E97">
-        <v>30.13</v>
+        <v>30.764</v>
       </c>
       <c r="F97">
-        <v>60.23</v>
+        <v>60.864</v>
       </c>
       <c r="G97">
         <v>3.24</v>
@@ -9229,37 +9229,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M97">
-        <v>14.202234</v>
+        <v>14.3517312</v>
       </c>
       <c r="N97">
-        <v>-9.455567333333335</v>
+        <v>-9.605064533333334</v>
       </c>
       <c r="O97">
-        <v>-2.174780486666667</v>
+        <v>-2.209164842666667</v>
       </c>
       <c r="P97">
-        <v>-7.280786846666667</v>
+        <v>-7.395899690666667</v>
       </c>
       <c r="Q97">
-        <v>-4.460786846666667</v>
+        <v>-4.575899690666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.057903025168339</v>
+        <v>1.310928781460425</v>
       </c>
       <c r="T97">
-        <v>15.65691191202049</v>
+        <v>19.57113989002562</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0768705355321799</v>
+        <v>0.07606980078705303</v>
       </c>
       <c r="W97">
-        <v>0.217673927721512</v>
+        <v>0.2178627409744129</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3342197197051299</v>
+        <v>0.3307382642915349</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2615853825938533</v>
+        <v>0.2634853825938533</v>
       </c>
       <c r="C98">
-        <v>-42.62379828960887</v>
+        <v>-43.3887229429326</v>
       </c>
       <c r="D98">
-        <v>15.00020171039112</v>
+        <v>14.86927705706739</v>
       </c>
       <c r="E98">
-        <v>30.764</v>
+        <v>31.398</v>
       </c>
       <c r="F98">
-        <v>60.864</v>
+        <v>61.498</v>
       </c>
       <c r="G98">
         <v>3.24</v>
@@ -9311,37 +9311,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M98">
-        <v>14.3517312</v>
+        <v>14.5012284</v>
       </c>
       <c r="N98">
-        <v>-9.605064533333334</v>
+        <v>-9.754561733333333</v>
       </c>
       <c r="O98">
-        <v>-2.209164842666667</v>
+        <v>-2.243549198666666</v>
       </c>
       <c r="P98">
-        <v>-7.395899690666667</v>
+        <v>-7.511012534666666</v>
       </c>
       <c r="Q98">
-        <v>-4.575899690666667</v>
+        <v>-4.691012534666665</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.310928781460421</v>
+        <v>1.732638375280562</v>
       </c>
       <c r="T98">
-        <v>19.57113989002556</v>
+        <v>26.09485318670076</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07606980078705303</v>
+        <v>0.07528557603667103</v>
       </c>
       <c r="W98">
-        <v>0.2178627409744129</v>
+        <v>0.218047661170553</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3307382642915349</v>
+        <v>0.3273285914637871</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2634853825938533</v>
+        <v>0.2653853825938533</v>
       </c>
       <c r="C99">
-        <v>-43.3887229429326</v>
+        <v>-44.15138190044019</v>
       </c>
       <c r="D99">
-        <v>14.86927705706739</v>
+        <v>14.74061809955982</v>
       </c>
       <c r="E99">
-        <v>31.398</v>
+        <v>32.032</v>
       </c>
       <c r="F99">
-        <v>61.498</v>
+        <v>62.132</v>
       </c>
       <c r="G99">
         <v>3.24</v>
@@ -9393,37 +9393,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M99">
-        <v>14.5012284</v>
+        <v>14.6507256</v>
       </c>
       <c r="N99">
-        <v>-9.754561733333333</v>
+        <v>-9.904058933333332</v>
       </c>
       <c r="O99">
-        <v>-2.243549198666666</v>
+        <v>-2.277933554666666</v>
       </c>
       <c r="P99">
-        <v>-7.511012534666666</v>
+        <v>-7.626125378666665</v>
       </c>
       <c r="Q99">
-        <v>-4.691012534666665</v>
+        <v>-4.806125378666665</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.732638375280562</v>
+        <v>2.576057562920842</v>
       </c>
       <c r="T99">
-        <v>26.09485318670076</v>
+        <v>39.14227978005113</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07528557603667103</v>
+        <v>0.07451735587303154</v>
       </c>
       <c r="W99">
-        <v>0.218047661170553</v>
+        <v>0.2182288074851392</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3273285914637871</v>
+        <v>0.3239885037957894</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2653853825938533</v>
+        <v>0.2672853825938533</v>
       </c>
       <c r="C100">
-        <v>-44.15138190044019</v>
+        <v>-44.91183347056715</v>
       </c>
       <c r="D100">
-        <v>14.74061809955982</v>
+        <v>14.61416652943285</v>
       </c>
       <c r="E100">
-        <v>32.032</v>
+        <v>32.666</v>
       </c>
       <c r="F100">
-        <v>62.132</v>
+        <v>62.766</v>
       </c>
       <c r="G100">
         <v>3.24</v>
@@ -9475,37 +9475,37 @@
         <v>4.746666666666667</v>
       </c>
       <c r="M100">
-        <v>14.6507256</v>
+        <v>14.8002228</v>
       </c>
       <c r="N100">
-        <v>-9.904058933333332</v>
+        <v>-10.05355613333333</v>
       </c>
       <c r="O100">
-        <v>-2.277933554666666</v>
+        <v>-2.312317910666667</v>
       </c>
       <c r="P100">
-        <v>-7.626125378666665</v>
+        <v>-7.741238222666667</v>
       </c>
       <c r="Q100">
-        <v>-4.806125378666665</v>
+        <v>-4.921238222666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.576057562920842</v>
+        <v>5.106315125841684</v>
       </c>
       <c r="T100">
-        <v>39.14227978005113</v>
+        <v>78.28455956010225</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07451735587303154</v>
+        <v>0.07376465530865749</v>
       </c>
       <c r="W100">
-        <v>0.2182288074851392</v>
+        <v>0.2184062942782186</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3239885037957894</v>
+        <v>0.3207158926463368</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2672853825938533</v>
-      </c>
-      <c r="C101">
-        <v>-44.91183347056715</v>
-      </c>
-      <c r="D101">
-        <v>14.61416652943285</v>
-      </c>
-      <c r="E101">
-        <v>32.666</v>
-      </c>
-      <c r="F101">
-        <v>62.766</v>
-      </c>
-      <c r="G101">
-        <v>3.24</v>
-      </c>
-      <c r="H101">
-        <v>33.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.566666666666667</v>
-      </c>
-      <c r="K101">
-        <v>2.82</v>
-      </c>
-      <c r="L101">
-        <v>4.746666666666667</v>
-      </c>
-      <c r="M101">
-        <v>14.8002228</v>
-      </c>
-      <c r="N101">
-        <v>-10.05355613333333</v>
-      </c>
-      <c r="O101">
-        <v>-2.312317910666667</v>
-      </c>
-      <c r="P101">
-        <v>-7.741238222666667</v>
-      </c>
-      <c r="Q101">
-        <v>-4.921238222666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.106315125841684</v>
-      </c>
-      <c r="T101">
-        <v>78.28455956010225</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07376465530865749</v>
-      </c>
-      <c r="W101">
-        <v>0.2184062942782186</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3207158926463368</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
